--- a/Inputs/F_template_parameters_Model.xlsx
+++ b/Inputs/F_template_parameters_Model.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usepa-my.sharepoint.com/personal/schlosser_paul_epa_gov/Documents/mcsim-5.6.5/PBPK_Model_Template_Mod/Inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="79" documentId="8_{7F8D94C6-EC2B-4A79-A22A-AD1B7807B962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30F759E8-85C1-4626-9B42-4EAF079863C5}"/>
+  <xr:revisionPtr revIDLastSave="88" documentId="8_{7F8D94C6-EC2B-4A79-A22A-AD1B7807B962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4DBCB10-2B19-4233-AED1-500595C89476}"/>
   <bookViews>
-    <workbookView xWindow="-25515" yWindow="885" windowWidth="21825" windowHeight="12915" xr2:uid="{089E7848-11EB-427A-89EA-83825F220BA0}"/>
+    <workbookView xWindow="1005" yWindow="0" windowWidth="23325" windowHeight="14910" activeTab="1" xr2:uid="{089E7848-11EB-427A-89EA-83825F220BA0}"/>
   </bookViews>
   <sheets>
-    <sheet name="Parameter_Set_1" sheetId="9" r:id="rId1"/>
+    <sheet name="Human4yo" sheetId="9" r:id="rId1"/>
+    <sheet name="Human8yo" sheetId="10" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="265">
   <si>
     <t>Code</t>
   </si>
@@ -809,9 +810,6 @@
     <t>tissue compartment 1 volume fraction ("rapidy perfused")</t>
   </si>
   <si>
-    <t>.</t>
-  </si>
-  <si>
     <t>Calculated, 1 - others</t>
   </si>
   <si>
@@ -828,6 +826,9 @@
   </si>
   <si>
     <t>Jean et al. used 0.05 for children, 0.03 for adults</t>
+  </si>
+  <si>
+    <t>ug</t>
   </si>
 </sst>
 </file>
@@ -899,7 +900,67 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="12">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1275,21 +1336,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ADCAA70-43B6-4F02-AE2A-67A6EACE5958}">
   <dimension ref="A1:J105"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="15.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.29296875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="51" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" customWidth="1"/>
-    <col min="5" max="5" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.41015625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.1171875" customWidth="1"/>
+    <col min="5" max="5" width="22.29296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.29296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.41015625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.5859375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.5703125" customWidth="1"/>
+    <col min="10" max="10" width="13.5859375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1309,7 +1370,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1320,7 +1381,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -1328,7 +1389,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -1336,7 +1397,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
@@ -1353,7 +1414,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -1370,7 +1431,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
@@ -1384,7 +1445,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A8" s="1" t="s">
         <v>20</v>
       </c>
@@ -1401,7 +1462,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A9" s="1" t="s">
         <v>245</v>
       </c>
@@ -1416,7 +1477,7 @@
       </c>
       <c r="E9" s="2"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A10" s="1" t="s">
         <v>132</v>
       </c>
@@ -1430,7 +1491,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A11" s="1" t="s">
         <v>133</v>
       </c>
@@ -1444,7 +1505,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A12" s="1" t="s">
         <v>174</v>
       </c>
@@ -1461,7 +1522,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A13" s="1" t="s">
         <v>178</v>
       </c>
@@ -1478,7 +1539,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A14" s="1" t="s">
         <v>164</v>
       </c>
@@ -1492,7 +1553,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A15" s="1" t="s">
         <v>192</v>
       </c>
@@ -1507,7 +1568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A16" s="1" t="s">
         <v>195</v>
       </c>
@@ -1522,7 +1583,7 @@
         <v>0.96</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A18" s="1" t="s">
         <v>0</v>
       </c>
@@ -1539,7 +1600,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A19" s="1" t="s">
         <v>69</v>
       </c>
@@ -1559,7 +1620,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A20" s="1" t="s">
         <v>27</v>
       </c>
@@ -1573,7 +1634,7 @@
         <v>0.74</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A21" s="1" t="s">
         <v>29</v>
       </c>
@@ -1583,11 +1644,8 @@
       <c r="D21">
         <v>0.75</v>
       </c>
-      <c r="E21" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A22" s="1" t="s">
         <v>226</v>
       </c>
@@ -1601,7 +1659,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A23" s="1" t="s">
         <v>31</v>
       </c>
@@ -1612,7 +1670,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A24" s="1" t="s">
         <v>32</v>
       </c>
@@ -1630,10 +1688,10 @@
         <v>15</v>
       </c>
       <c r="F24" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A25" s="1" t="s">
         <v>42</v>
       </c>
@@ -1644,7 +1702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A26" s="1" t="s">
         <v>138</v>
       </c>
@@ -1668,7 +1726,7 @@
       <c r="I26" s="4"/>
       <c r="J26" s="4"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A27" s="1" t="s">
         <v>139</v>
       </c>
@@ -1693,7 +1751,7 @@
       <c r="I27" s="4"/>
       <c r="J27" s="4"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A28" s="1" t="s">
         <v>47</v>
       </c>
@@ -1717,7 +1775,7 @@
       <c r="I28" s="4"/>
       <c r="J28" s="4"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A29" s="1" t="s">
         <v>140</v>
       </c>
@@ -1741,7 +1799,7 @@
       <c r="I29" s="4"/>
       <c r="J29" s="4"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A30" s="1" t="s">
         <v>141</v>
       </c>
@@ -1765,7 +1823,7 @@
       <c r="I30" s="4"/>
       <c r="J30" s="4"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A31" s="1" t="s">
         <v>142</v>
       </c>
@@ -1779,7 +1837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A32" s="1" t="s">
         <v>51</v>
       </c>
@@ -1796,7 +1854,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A33" s="1" t="s">
         <v>52</v>
       </c>
@@ -1810,7 +1868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A34" s="1" t="s">
         <v>53</v>
       </c>
@@ -1824,7 +1882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A35" s="1" t="s">
         <v>54</v>
       </c>
@@ -1838,7 +1896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A36" s="1" t="s">
         <v>165</v>
       </c>
@@ -1859,7 +1917,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A37" s="1" t="s">
         <v>56</v>
       </c>
@@ -1873,7 +1931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A38" s="1" t="s">
         <v>237</v>
       </c>
@@ -1887,7 +1945,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A39" s="1" t="s">
         <v>236</v>
       </c>
@@ -1901,7 +1959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A40" s="1" t="s">
         <v>238</v>
       </c>
@@ -1915,7 +1973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A41" s="1" t="s">
         <v>143</v>
       </c>
@@ -1932,7 +1990,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A42" s="1" t="s">
         <v>144</v>
       </c>
@@ -1946,7 +2004,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A43" s="1" t="s">
         <v>145</v>
       </c>
@@ -1960,7 +2018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A44" s="1" t="s">
         <v>146</v>
       </c>
@@ -1977,7 +2035,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A45" s="1" t="s">
         <v>147</v>
       </c>
@@ -1991,7 +2049,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A46" s="1" t="s">
         <v>203</v>
       </c>
@@ -2009,7 +2067,7 @@
         <v>8.3312089894352168E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A47" s="1" t="s">
         <v>148</v>
       </c>
@@ -2026,7 +2084,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A48" s="1" t="s">
         <v>149</v>
       </c>
@@ -2040,7 +2098,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A49" s="1" t="s">
         <v>150</v>
       </c>
@@ -2054,7 +2112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A50" s="1" t="s">
         <v>37</v>
       </c>
@@ -2065,7 +2123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A51" s="1" t="s">
         <v>168</v>
       </c>
@@ -2076,7 +2134,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A52" s="1" t="s">
         <v>39</v>
       </c>
@@ -2087,7 +2145,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A53" s="1" t="s">
         <v>184</v>
       </c>
@@ -2101,7 +2159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A54" s="1" t="s">
         <v>160</v>
       </c>
@@ -2115,7 +2173,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A55" s="1" t="s">
         <v>161</v>
       </c>
@@ -2126,7 +2184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A56" s="1" t="s">
         <v>198</v>
       </c>
@@ -2140,7 +2198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A57" s="1" t="s">
         <v>200</v>
       </c>
@@ -2154,7 +2212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A58" s="1" t="s">
         <v>231</v>
       </c>
@@ -2171,7 +2229,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A59" s="1" t="s">
         <v>41</v>
       </c>
@@ -2182,7 +2240,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A61" s="1" t="s">
         <v>0</v>
       </c>
@@ -2199,7 +2257,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A62" s="1" t="s">
         <v>79</v>
       </c>
@@ -2216,7 +2274,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A63" s="1" t="s">
         <v>134</v>
       </c>
@@ -2233,7 +2291,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A64" s="1" t="s">
         <v>136</v>
       </c>
@@ -2250,7 +2308,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A65" s="1" t="s">
         <v>82</v>
       </c>
@@ -2267,7 +2325,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A66" s="1" t="s">
         <v>89</v>
       </c>
@@ -2284,7 +2342,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A67" s="1" t="s">
         <v>90</v>
       </c>
@@ -2304,7 +2362,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A68" s="1" t="s">
         <v>91</v>
       </c>
@@ -2324,7 +2382,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A69" s="1" t="s">
         <v>92</v>
       </c>
@@ -2341,7 +2399,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A70" s="1" t="s">
         <v>93</v>
       </c>
@@ -2358,10 +2416,10 @@
         <v>3.5999999999999997E-2</v>
       </c>
       <c r="F70" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A71" s="1" t="s">
         <v>94</v>
       </c>
@@ -2378,7 +2436,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A72" s="1" t="s">
         <v>95</v>
       </c>
@@ -2395,7 +2453,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A73" s="1" t="s">
         <v>96</v>
       </c>
@@ -2412,7 +2470,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A74" s="1" t="s">
         <v>97</v>
       </c>
@@ -2429,7 +2487,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A75" s="1" t="s">
         <v>98</v>
       </c>
@@ -2449,7 +2507,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A76" s="1" t="s">
         <v>151</v>
       </c>
@@ -2469,7 +2527,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A77" s="1" t="s">
         <v>104</v>
       </c>
@@ -2486,7 +2544,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A78" s="1" t="s">
         <v>105</v>
       </c>
@@ -2506,7 +2564,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A79" s="1" t="s">
         <v>106</v>
       </c>
@@ -2526,7 +2584,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A80" s="1" t="s">
         <v>107</v>
       </c>
@@ -2543,10 +2601,10 @@
         <v>0.36</v>
       </c>
       <c r="F80" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A81" s="1" t="s">
         <v>108</v>
       </c>
@@ -2563,7 +2621,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A82" s="1" t="s">
         <v>109</v>
       </c>
@@ -2580,7 +2638,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A83" s="1" t="s">
         <v>110</v>
       </c>
@@ -2597,7 +2655,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A84" s="1" t="s">
         <v>111</v>
       </c>
@@ -2614,12 +2672,12 @@
         <v>223</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A85" s="1" t="s">
         <v>112</v>
       </c>
       <c r="B85" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C85" t="s">
         <v>185</v>
@@ -2631,16 +2689,16 @@
         <v>0.05</v>
       </c>
       <c r="F85" t="s">
+        <v>262</v>
+      </c>
+      <c r="G85" s="6" t="s">
         <v>263</v>
-      </c>
-      <c r="G85" s="6" t="s">
-        <v>264</v>
       </c>
       <c r="H85" s="6"/>
       <c r="I85" s="6"/>
       <c r="J85" s="6"/>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A86" s="1" t="s">
         <v>153</v>
       </c>
@@ -2661,11 +2719,11 @@
         <v>225</v>
       </c>
       <c r="G86" s="5" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H86" s="5"/>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A87" s="1" t="s">
         <v>121</v>
       </c>
@@ -2679,7 +2737,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A88" s="1" t="s">
         <v>122</v>
       </c>
@@ -2693,7 +2751,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A89" s="1" t="s">
         <v>123</v>
       </c>
@@ -2710,7 +2768,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A90" s="1" t="s">
         <v>124</v>
       </c>
@@ -2727,7 +2785,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A91" s="1" t="s">
         <v>125</v>
       </c>
@@ -2741,10 +2799,10 @@
         <v>0.83</v>
       </c>
       <c r="F91" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A92" s="1" t="s">
         <v>126</v>
       </c>
@@ -2758,7 +2816,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A93" s="1" t="s">
         <v>127</v>
       </c>
@@ -2772,7 +2830,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A94" s="1" t="s">
         <v>128</v>
       </c>
@@ -2786,7 +2844,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A95" s="1" t="s">
         <v>129</v>
       </c>
@@ -2800,7 +2858,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A96" s="1" t="s">
         <v>130</v>
       </c>
@@ -2817,7 +2875,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A97" s="1" t="s">
         <v>156</v>
       </c>
@@ -2834,7 +2892,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A99" s="1" t="s">
         <v>0</v>
       </c>
@@ -2851,7 +2909,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A100" s="1" t="s">
         <v>34</v>
       </c>
@@ -2859,7 +2917,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A102" s="1" t="s">
         <v>0</v>
       </c>
@@ -2874,7 +2932,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A103" s="1" t="s">
         <v>73</v>
       </c>
@@ -2882,7 +2940,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A104" s="1" t="s">
         <v>75</v>
       </c>
@@ -2890,7 +2948,1659 @@
         <v>76</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A105" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B105" t="s">
+        <v>78</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="E15">
+    <cfRule type="cellIs" dxfId="11" priority="4" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="5" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="9" priority="6" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E16">
+    <cfRule type="cellIs" dxfId="8" priority="1" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="greaterThan">
+      <formula>1.2</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="3" operator="between">
+      <formula>0.8</formula>
+      <formula>1.2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2530FCFD-82CD-436F-B981-3C7AACA19280}">
+  <dimension ref="A1:J105"/>
+  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <cols>
+    <col min="1" max="1" width="15.29296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="51" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.41015625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.1171875" customWidth="1"/>
+    <col min="5" max="5" width="22.29296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.29296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.41015625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.5859375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.5859375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>264</v>
+      </c>
+      <c r="F5" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" t="s">
+        <v>248</v>
+      </c>
+      <c r="F6" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" t="s">
+        <v>182</v>
+      </c>
+      <c r="F8" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A9" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="2">
+        <v>2</v>
+      </c>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A10" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B10" t="s">
+        <v>176</v>
+      </c>
+      <c r="C10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A11" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B11" t="s">
+        <v>177</v>
+      </c>
+      <c r="C11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A12" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B12" t="s">
+        <v>175</v>
+      </c>
+      <c r="C12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" t="s">
+        <v>182</v>
+      </c>
+      <c r="F12" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A13" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B13" t="s">
+        <v>179</v>
+      </c>
+      <c r="C13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" t="s">
+        <v>182</v>
+      </c>
+      <c r="E13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A14" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B14" t="s">
+        <v>159</v>
+      </c>
+      <c r="C14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A15" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B15" t="s">
+        <v>193</v>
+      </c>
+      <c r="C15" t="s">
+        <v>194</v>
+      </c>
+      <c r="E15">
+        <f>1-SUM(E77:E86)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A16" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B16" t="s">
+        <v>196</v>
+      </c>
+      <c r="C16" t="s">
+        <v>197</v>
+      </c>
+      <c r="E16">
+        <f>SUM(E62:E76)</f>
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.5">
+      <c r="A18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.5">
+      <c r="A19" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B19" t="s">
+        <v>70</v>
+      </c>
+      <c r="C19" t="s">
+        <v>71</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>19</v>
+      </c>
+      <c r="F19" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.5">
+      <c r="A20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20">
+        <v>0.75</v>
+      </c>
+      <c r="E20">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.5">
+      <c r="A21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.5">
+      <c r="A22" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B22" t="s">
+        <v>227</v>
+      </c>
+      <c r="D22">
+        <v>-0.25</v>
+      </c>
+      <c r="F22" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.5">
+      <c r="A23" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B23" t="s">
+        <v>228</v>
+      </c>
+      <c r="D23">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.5">
+      <c r="A24" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" t="s">
+        <v>188</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <f>360/24</f>
+        <v>15</v>
+      </c>
+      <c r="F24" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.5">
+      <c r="A25" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B25" t="s">
+        <v>43</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.5">
+      <c r="A26" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C26" t="s">
+        <v>189</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3"/>
+      <c r="F26" s="4">
+        <v>8</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.5">
+      <c r="A27" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B27" t="s">
+        <v>45</v>
+      </c>
+      <c r="C27" t="s">
+        <v>46</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27" s="3"/>
+      <c r="F27" s="4">
+        <f>2.9*60/1000</f>
+        <v>0.17399999999999999</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.5">
+      <c r="A28" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B28" t="s">
+        <v>48</v>
+      </c>
+      <c r="C28" t="s">
+        <v>190</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="F28" s="4">
+        <f>F27/(70^0.75)</f>
+        <v>7.1899474840331325E-3</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.5">
+      <c r="A29" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B29" t="s">
+        <v>49</v>
+      </c>
+      <c r="C29" t="s">
+        <v>190</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="F29" s="4">
+        <f>0.1 + 0.4*F26/18</f>
+        <v>0.27777777777777779</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.5">
+      <c r="A30" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B30" t="s">
+        <v>208</v>
+      </c>
+      <c r="C30" t="s">
+        <v>36</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="F30" s="4">
+        <f>0.9-0.4*F26/18</f>
+        <v>0.72222222222222221</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.5">
+      <c r="A31" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B31" t="s">
+        <v>50</v>
+      </c>
+      <c r="C31" t="s">
+        <v>190</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.5">
+      <c r="A32" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B32" t="s">
+        <v>205</v>
+      </c>
+      <c r="C32" t="s">
+        <v>36</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="F32" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A33" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B33" t="s">
+        <v>206</v>
+      </c>
+      <c r="C33" t="s">
+        <v>36</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A34" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B34" t="s">
+        <v>207</v>
+      </c>
+      <c r="C34" t="s">
+        <v>36</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A35" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B35" t="s">
+        <v>55</v>
+      </c>
+      <c r="C35" t="s">
+        <v>36</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A36" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B36" t="s">
+        <v>166</v>
+      </c>
+      <c r="C36" t="s">
+        <v>190</v>
+      </c>
+      <c r="D36">
+        <v>0</v>
+      </c>
+      <c r="E36" s="4">
+        <f>F28*F29</f>
+        <v>1.997207634453648E-3</v>
+      </c>
+      <c r="F36" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A37" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B37" t="s">
+        <v>167</v>
+      </c>
+      <c r="C37" t="s">
+        <v>190</v>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A38" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B38" t="s">
+        <v>57</v>
+      </c>
+      <c r="C38" t="s">
+        <v>46</v>
+      </c>
+      <c r="D38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A39" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B39" t="s">
+        <v>58</v>
+      </c>
+      <c r="C39" t="s">
+        <v>59</v>
+      </c>
+      <c r="D39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A40" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B40" t="s">
+        <v>60</v>
+      </c>
+      <c r="C40" t="s">
+        <v>36</v>
+      </c>
+      <c r="D40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A41" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B41" t="s">
+        <v>61</v>
+      </c>
+      <c r="C41" t="s">
+        <v>189</v>
+      </c>
+      <c r="D41">
+        <v>0</v>
+      </c>
+      <c r="F41" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A42" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B42" t="s">
+        <v>62</v>
+      </c>
+      <c r="C42" t="s">
+        <v>46</v>
+      </c>
+      <c r="D42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A43" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B43" t="s">
+        <v>63</v>
+      </c>
+      <c r="C43" t="s">
+        <v>244</v>
+      </c>
+      <c r="D43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A44" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B44" t="s">
+        <v>64</v>
+      </c>
+      <c r="C44" t="s">
+        <v>189</v>
+      </c>
+      <c r="D44">
+        <v>0</v>
+      </c>
+      <c r="F44" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A45" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B45" t="s">
+        <v>65</v>
+      </c>
+      <c r="C45" t="s">
+        <v>46</v>
+      </c>
+      <c r="D45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A46" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B46" t="s">
+        <v>204</v>
+      </c>
+      <c r="C46" t="s">
+        <v>244</v>
+      </c>
+      <c r="D46">
+        <v>0</v>
+      </c>
+      <c r="E46" s="4">
+        <f>F28*F30/E75</f>
+        <v>7.4181997851135495E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A47" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B47" t="s">
+        <v>66</v>
+      </c>
+      <c r="C47" t="s">
+        <v>189</v>
+      </c>
+      <c r="D47">
+        <v>0</v>
+      </c>
+      <c r="F47" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A48" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B48" t="s">
+        <v>67</v>
+      </c>
+      <c r="C48" t="s">
+        <v>46</v>
+      </c>
+      <c r="D48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A49" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B49" t="s">
+        <v>68</v>
+      </c>
+      <c r="C49" t="s">
+        <v>244</v>
+      </c>
+      <c r="D49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A50" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B50" t="s">
+        <v>38</v>
+      </c>
+      <c r="D50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A51" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B51" t="s">
+        <v>169</v>
+      </c>
+      <c r="D51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A52" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B52" t="s">
+        <v>40</v>
+      </c>
+      <c r="D52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A53" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B53" t="s">
+        <v>183</v>
+      </c>
+      <c r="C53" t="s">
+        <v>185</v>
+      </c>
+      <c r="D53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A54" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B54" t="s">
+        <v>162</v>
+      </c>
+      <c r="C54" t="s">
+        <v>191</v>
+      </c>
+      <c r="D54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A55" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B55" t="s">
+        <v>163</v>
+      </c>
+      <c r="D55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A56" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B56" t="s">
+        <v>199</v>
+      </c>
+      <c r="C56" t="s">
+        <v>36</v>
+      </c>
+      <c r="D56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A57" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B57" t="s">
+        <v>201</v>
+      </c>
+      <c r="C57" t="s">
+        <v>202</v>
+      </c>
+      <c r="D57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A58" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B58" t="s">
+        <v>232</v>
+      </c>
+      <c r="C58" t="s">
+        <v>234</v>
+      </c>
+      <c r="D58">
+        <v>0</v>
+      </c>
+      <c r="F58" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A59" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B59" t="s">
+        <v>242</v>
+      </c>
+      <c r="D59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A61" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A62" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B62" t="s">
+        <v>80</v>
+      </c>
+      <c r="C62" t="s">
+        <v>186</v>
+      </c>
+      <c r="D62">
+        <v>1</v>
+      </c>
+      <c r="F62" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A63" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B63" t="s">
+        <v>135</v>
+      </c>
+      <c r="C63" t="s">
+        <v>186</v>
+      </c>
+      <c r="D63">
+        <v>1</v>
+      </c>
+      <c r="F63" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A64" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B64" t="s">
+        <v>137</v>
+      </c>
+      <c r="C64" t="s">
+        <v>186</v>
+      </c>
+      <c r="D64">
+        <v>1</v>
+      </c>
+      <c r="F64" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A65" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B65" t="s">
+        <v>81</v>
+      </c>
+      <c r="C65" t="s">
+        <v>186</v>
+      </c>
+      <c r="D65">
+        <v>1</v>
+      </c>
+      <c r="F65" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A66" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B66" t="s">
+        <v>209</v>
+      </c>
+      <c r="C66" t="s">
+        <v>186</v>
+      </c>
+      <c r="D66">
+        <v>1</v>
+      </c>
+      <c r="F66" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A67" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B67" t="s">
+        <v>83</v>
+      </c>
+      <c r="C67" t="s">
+        <v>186</v>
+      </c>
+      <c r="D67">
+        <v>1</v>
+      </c>
+      <c r="E67">
+        <v>0.03</v>
+      </c>
+      <c r="F67" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A68" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B68" t="s">
+        <v>84</v>
+      </c>
+      <c r="C68" t="s">
+        <v>186</v>
+      </c>
+      <c r="D68">
+        <v>1</v>
+      </c>
+      <c r="E68">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="F68" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A69" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B69" t="s">
+        <v>85</v>
+      </c>
+      <c r="C69" t="s">
+        <v>186</v>
+      </c>
+      <c r="D69">
+        <v>1</v>
+      </c>
+      <c r="F69" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A70" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B70" t="s">
+        <v>257</v>
+      </c>
+      <c r="C70" t="s">
+        <v>186</v>
+      </c>
+      <c r="D70">
+        <v>1</v>
+      </c>
+      <c r="E70">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="F70" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A71" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B71" t="s">
+        <v>152</v>
+      </c>
+      <c r="C71" t="s">
+        <v>186</v>
+      </c>
+      <c r="D71">
+        <v>1</v>
+      </c>
+      <c r="F71" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A72" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B72" t="s">
+        <v>86</v>
+      </c>
+      <c r="C72" t="s">
+        <v>186</v>
+      </c>
+      <c r="D72">
+        <v>1</v>
+      </c>
+      <c r="F72" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A73" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B73" t="s">
+        <v>87</v>
+      </c>
+      <c r="C73" t="s">
+        <v>186</v>
+      </c>
+      <c r="D73">
+        <v>1</v>
+      </c>
+      <c r="F73" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A74" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B74" t="s">
+        <v>88</v>
+      </c>
+      <c r="C74" t="s">
+        <v>186</v>
+      </c>
+      <c r="D74">
+        <v>1</v>
+      </c>
+      <c r="F74" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A75" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B75" t="s">
+        <v>255</v>
+      </c>
+      <c r="C75" t="s">
+        <v>186</v>
+      </c>
+      <c r="D75">
+        <v>1</v>
+      </c>
+      <c r="E75">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="F75" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A76" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B76" t="s">
+        <v>256</v>
+      </c>
+      <c r="C76" t="s">
+        <v>186</v>
+      </c>
+      <c r="D76">
+        <v>1</v>
+      </c>
+      <c r="E76">
+        <v>0.82</v>
+      </c>
+      <c r="F76" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A77" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B77" t="s">
+        <v>210</v>
+      </c>
+      <c r="C77" t="s">
+        <v>185</v>
+      </c>
+      <c r="D77">
+        <v>0</v>
+      </c>
+      <c r="F77" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A78" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B78" t="s">
+        <v>99</v>
+      </c>
+      <c r="C78" t="s">
+        <v>185</v>
+      </c>
+      <c r="D78">
+        <v>0</v>
+      </c>
+      <c r="E78">
+        <v>0.24</v>
+      </c>
+      <c r="F78" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A79" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B79" t="s">
+        <v>100</v>
+      </c>
+      <c r="C79" t="s">
+        <v>185</v>
+      </c>
+      <c r="D79">
+        <v>0</v>
+      </c>
+      <c r="E79">
+        <v>0.15</v>
+      </c>
+      <c r="F79" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A80" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B80" t="s">
+        <v>173</v>
+      </c>
+      <c r="C80" t="s">
+        <v>185</v>
+      </c>
+      <c r="D80">
+        <v>0</v>
+      </c>
+      <c r="E80">
+        <v>0.36</v>
+      </c>
+      <c r="F80" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.5">
+      <c r="A81" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B81" t="s">
+        <v>155</v>
+      </c>
+      <c r="C81" t="s">
+        <v>185</v>
+      </c>
+      <c r="D81">
+        <v>0</v>
+      </c>
+      <c r="F81" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.5">
+      <c r="A82" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B82" t="s">
+        <v>101</v>
+      </c>
+      <c r="C82" t="s">
+        <v>185</v>
+      </c>
+      <c r="D82">
+        <v>0</v>
+      </c>
+      <c r="F82" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.5">
+      <c r="A83" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B83" t="s">
+        <v>102</v>
+      </c>
+      <c r="C83" t="s">
+        <v>185</v>
+      </c>
+      <c r="D83">
+        <v>0</v>
+      </c>
+      <c r="F83" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.5">
+      <c r="A84" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B84" t="s">
+        <v>103</v>
+      </c>
+      <c r="C84" t="s">
+        <v>185</v>
+      </c>
+      <c r="D84">
+        <v>0</v>
+      </c>
+      <c r="F84" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.5">
+      <c r="A85" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B85" t="s">
+        <v>259</v>
+      </c>
+      <c r="C85" t="s">
+        <v>185</v>
+      </c>
+      <c r="D85">
+        <v>0</v>
+      </c>
+      <c r="E85" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="F85" t="s">
+        <v>262</v>
+      </c>
+      <c r="G85" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="H85" s="6"/>
+      <c r="I85" s="6"/>
+      <c r="J85" s="6"/>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.5">
+      <c r="A86" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B86" t="s">
+        <v>154</v>
+      </c>
+      <c r="C86" t="s">
+        <v>185</v>
+      </c>
+      <c r="D86">
+        <v>0</v>
+      </c>
+      <c r="E86" s="5">
+        <f>1-SUM(E78:E85)</f>
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="F86" t="s">
+        <v>225</v>
+      </c>
+      <c r="G86" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="H86" s="5"/>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.5">
+      <c r="A87" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B87" t="s">
+        <v>113</v>
+      </c>
+      <c r="D87">
+        <v>1</v>
+      </c>
+      <c r="F87" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.5">
+      <c r="A88" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B88" t="s">
+        <v>211</v>
+      </c>
+      <c r="D88">
+        <v>1</v>
+      </c>
+      <c r="F88" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.5">
+      <c r="A89" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B89" t="s">
+        <v>114</v>
+      </c>
+      <c r="D89">
+        <v>1</v>
+      </c>
+      <c r="E89">
+        <v>0.98</v>
+      </c>
+      <c r="F89" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.5">
+      <c r="A90" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B90" t="s">
+        <v>115</v>
+      </c>
+      <c r="D90">
+        <v>1</v>
+      </c>
+      <c r="E90">
+        <v>4.16</v>
+      </c>
+      <c r="F90" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.5">
+      <c r="A91" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B91" t="s">
+        <v>172</v>
+      </c>
+      <c r="D91">
+        <v>1</v>
+      </c>
+      <c r="E91">
+        <v>0.83</v>
+      </c>
+      <c r="F91" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.5">
+      <c r="A92" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B92" t="s">
+        <v>158</v>
+      </c>
+      <c r="D92">
+        <v>1</v>
+      </c>
+      <c r="F92" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.5">
+      <c r="A93" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B93" t="s">
+        <v>116</v>
+      </c>
+      <c r="D93">
+        <v>1</v>
+      </c>
+      <c r="F93" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.5">
+      <c r="A94" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B94" t="s">
+        <v>117</v>
+      </c>
+      <c r="D94">
+        <v>1</v>
+      </c>
+      <c r="F94" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.5">
+      <c r="A95" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B95" t="s">
+        <v>118</v>
+      </c>
+      <c r="D95">
+        <v>1</v>
+      </c>
+      <c r="F95" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.5">
+      <c r="A96" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B96" t="s">
+        <v>131</v>
+      </c>
+      <c r="D96">
+        <v>1</v>
+      </c>
+      <c r="E96">
+        <v>1000</v>
+      </c>
+      <c r="F96" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A97" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B97" t="s">
+        <v>157</v>
+      </c>
+      <c r="D97">
+        <v>1</v>
+      </c>
+      <c r="E97">
+        <v>0.63</v>
+      </c>
+      <c r="F97" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A99" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A100" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B100" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A102" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D102" s="1"/>
+      <c r="E102" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A103" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B103" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A104" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B104" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A105" s="1" t="s">
         <v>77</v>
       </c>
@@ -2928,20 +4638,51 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_Source xmlns="http://schemas.microsoft.com/sharepoint/v3/fields" xsi:nil="true"/>
+    <Language xmlns="http://schemas.microsoft.com/sharepoint/v3">English</Language>
+    <j747ac98061d40f0aa7bd47e1db5675d xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </j747ac98061d40f0aa7bd47e1db5675d>
+    <External_x0020_Contributor xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
+    <TaxKeywordTaxHTField xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </TaxKeywordTaxHTField>
+    <Record xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">Shared</Record>
+    <Rights xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
+    <Document_x0020_Creation_x0020_Date xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">2020-10-14T20:30:29+00:00</Document_x0020_Creation_x0020_Date>
+    <EPA_x0020_Office xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
+    <CategoryDescription xmlns="http://schemas.microsoft.com/sharepoint.v3" xsi:nil="true"/>
+    <Identifier xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
+    <_Coverage xmlns="http://schemas.microsoft.com/sharepoint/v3/fields" xsi:nil="true"/>
+    <Creator xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Creator>
+    <EPA_x0020_Related_x0020_Documents xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
+    <EPA_x0020_Contributor xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </EPA_x0020_Contributor>
+    <TaxCatchAll xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
+    <e3f09c3df709400db2417a7161762d62 xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </e3f09c3df709400db2417a7161762d62>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2ba80736-48fa-4d73-aaff-bacaeeed013a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="29f62856-1543-49d4-a736-4569d363f533" ContentTypeId="0x0101" PreviousValue="false"/>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C107526348C97345843FB1F7E3F5FF14" ma:contentTypeVersion="20" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1f5efa0b4590ceb4068c523eef838cbf">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xmlns:ns3="http://schemas.microsoft.com/sharepoint.v3" xmlns:ns4="http://schemas.microsoft.com/sharepoint/v3/fields" xmlns:ns5="2ba80736-48fa-4d73-aaff-bacaeeed013a" xmlns:ns6="41d9f072-86bf-4c63-b117-debf50ff4701" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9d32b47d5805bf9e4ccfb00021215c68" ns1:_="" ns2:_="" ns3:_="" ns4:_="" ns5:_="" ns6:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -3414,68 +5155,36 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="29f62856-1543-49d4-a736-4569d363f533" ContentTypeId="0x0101" PreviousValue="false"/>
+</file>
+
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Source xmlns="http://schemas.microsoft.com/sharepoint/v3/fields" xsi:nil="true"/>
-    <Language xmlns="http://schemas.microsoft.com/sharepoint/v3">English</Language>
-    <j747ac98061d40f0aa7bd47e1db5675d xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </j747ac98061d40f0aa7bd47e1db5675d>
-    <External_x0020_Contributor xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
-    <TaxKeywordTaxHTField xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </TaxKeywordTaxHTField>
-    <Record xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">Shared</Record>
-    <Rights xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
-    <Document_x0020_Creation_x0020_Date xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">2020-10-14T20:30:29+00:00</Document_x0020_Creation_x0020_Date>
-    <EPA_x0020_Office xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
-    <CategoryDescription xmlns="http://schemas.microsoft.com/sharepoint.v3" xsi:nil="true"/>
-    <Identifier xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
-    <_Coverage xmlns="http://schemas.microsoft.com/sharepoint/v3/fields" xsi:nil="true"/>
-    <Creator xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Creator>
-    <EPA_x0020_Related_x0020_Documents xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
-    <EPA_x0020_Contributor xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </EPA_x0020_Contributor>
-    <TaxCatchAll xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
-    <e3f09c3df709400db2417a7161762d62 xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </e3f09c3df709400db2417a7161762d62>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2ba80736-48fa-4d73-aaff-bacaeeed013a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4DC26B68-A11F-428F-9051-23DC6334A810}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA939294-F21F-45CD-81A6-3A616888DAC5}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/fields"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4"/>
+    <ds:schemaRef ds:uri="93237db7-bebb-43bb-9414-bc3313990c09"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint.v3"/>
+    <ds:schemaRef ds:uri="2ba80736-48fa-4d73-aaff-bacaeeed013a"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C4A2D8C-C5B5-46A0-8FC1-3730CC1A83D7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{90A172F1-773B-43BF-8B86-8CD1537A96AE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3498,17 +5207,18 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C4A2D8C-C5B5-46A0-8FC1-3730CC1A83D7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA939294-F21F-45CD-81A6-3A616888DAC5}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4DC26B68-A11F-428F-9051-23DC6334A810}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/fields"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4"/>
-    <ds:schemaRef ds:uri="93237db7-bebb-43bb-9414-bc3313990c09"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint.v3"/>
-    <ds:schemaRef ds:uri="2ba80736-48fa-4d73-aaff-bacaeeed013a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Inputs/F_template_parameters_Model.xlsx
+++ b/Inputs/F_template_parameters_Model.xlsx
@@ -8,14 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usepa-my.sharepoint.com/personal/schlosser_paul_epa_gov/Documents/mcsim-5.6.5/PBPK_Model_Template_Mod/Inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="88" documentId="8_{7F8D94C6-EC2B-4A79-A22A-AD1B7807B962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4DBCB10-2B19-4233-AED1-500595C89476}"/>
+  <xr:revisionPtr revIDLastSave="257" documentId="8_{7F8D94C6-EC2B-4A79-A22A-AD1B7807B962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9BAEC706-8C59-4BC2-9C2F-BEF881BFFAC2}"/>
   <bookViews>
-    <workbookView xWindow="1005" yWindow="0" windowWidth="23325" windowHeight="14910" activeTab="1" xr2:uid="{089E7848-11EB-427A-89EA-83825F220BA0}"/>
+    <workbookView xWindow="-23040" yWindow="45" windowWidth="25410" windowHeight="14640" xr2:uid="{089E7848-11EB-427A-89EA-83825F220BA0}"/>
   </bookViews>
   <sheets>
     <sheet name="Human4yo" sheetId="9" r:id="rId1"/>
     <sheet name="Human8yo" sheetId="10" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="age" localSheetId="0">Human4yo!$F$26</definedName>
+    <definedName name="BH" localSheetId="0">Human4yo!$H$25</definedName>
+    <definedName name="BW" localSheetId="0">Human4yo!$F$25</definedName>
+    <definedName name="BW" localSheetId="1">Human8yo!$F$25</definedName>
+    <definedName name="CLp" localSheetId="0">Human4yo!$F$27</definedName>
+    <definedName name="PC">Human4yo!$I$21</definedName>
+    <definedName name="Qct" localSheetId="0">Human4yo!$G$77</definedName>
+    <definedName name="surface" localSheetId="0">Human4yo!$H$26</definedName>
+    <definedName name="Vtf" localSheetId="0">Human4yo!$G$76</definedName>
+    <definedName name="Vtf">Human4yo!$I$12</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -33,8 +45,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="289">
   <si>
     <t>Code</t>
   </si>
@@ -786,18 +820,12 @@
     <t>h</t>
   </si>
   <si>
-    <t>Total plasma CL (L/h ~ kg/h; adult, Rao 1996)</t>
-  </si>
-  <si>
     <t>age (years)</t>
   </si>
   <si>
     <t>Fraction urinary clearance</t>
   </si>
   <si>
-    <t>(kg^0.25/h), " scaled to 70^0.75</t>
-  </si>
-  <si>
     <t>Fraction bone clearance</t>
   </si>
   <si>
@@ -829,12 +857,93 @@
   </si>
   <si>
     <t>ug</t>
+  </si>
+  <si>
+    <t>BW (kg)</t>
+  </si>
+  <si>
+    <t>(kg^0.25/h), " scaled to BW^0.75</t>
+  </si>
+  <si>
+    <t>&lt;= renal CL (L/h)</t>
+  </si>
+  <si>
+    <t>&lt;=bone CL (L/h)</t>
+  </si>
+  <si>
+    <t>Total plasma CL (L/h ~ kg/h; Jean 2016)</t>
+  </si>
+  <si>
+    <t>Tota urinary CL (L/h) V</t>
+  </si>
+  <si>
+    <t>&lt;= Total bone CL (L/h)</t>
+  </si>
+  <si>
+    <t>height (cm)</t>
+  </si>
+  <si>
+    <t>Total volumes</t>
+  </si>
+  <si>
+    <t>slowly perfused</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>&lt;= total Qc (L/h)</t>
+  </si>
+  <si>
+    <t>Slowly perfused</t>
+  </si>
+  <si>
+    <t>Volume</t>
+  </si>
+  <si>
+    <t>Tongue</t>
+  </si>
+  <si>
+    <t>Heart</t>
+  </si>
+  <si>
+    <t>Muscle</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Blood flows</t>
+  </si>
+  <si>
+    <t>Surface area (cm^2)</t>
+  </si>
+  <si>
+    <t>^ Vtf/"Total"</t>
+  </si>
+  <si>
+    <t>volume above</t>
+  </si>
+  <si>
+    <t>x Vtf/"Total" volume</t>
+  </si>
+  <si>
+    <t>^ "Total" blood flow above</t>
+  </si>
+  <si>
+    <t>Tissue:plasma coeffs</t>
+  </si>
+  <si>
+    <t>Below was copied, with limited translation, from the Jean et al. spreadsheet</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -876,10 +985,104 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -888,7 +1091,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -896,6 +1099,34 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1335,22 +1566,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ADCAA70-43B6-4F02-AE2A-67A6EACE5958}">
-  <dimension ref="A1:J105"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <dimension ref="A1:N105"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.29296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="51" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.41015625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.1171875" customWidth="1"/>
-    <col min="5" max="5" width="22.29296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.29296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.41015625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.5859375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" customWidth="1"/>
+    <col min="5" max="5" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.5859375" customWidth="1"/>
+    <col min="10" max="10" width="13.5703125" customWidth="1"/>
+    <col min="11" max="11" width="13.140625" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1370,7 +1603,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1381,7 +1614,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -1389,7 +1622,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -1397,7 +1630,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
@@ -1414,7 +1647,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -1431,7 +1664,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
@@ -1445,7 +1678,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>20</v>
       </c>
@@ -1462,7 +1695,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>245</v>
       </c>
@@ -1475,9 +1708,11 @@
       <c r="D9" s="2">
         <v>2</v>
       </c>
-      <c r="E9" s="2"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="E9" s="2" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>132</v>
       </c>
@@ -1490,8 +1725,11 @@
       <c r="D10" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="E10" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>133</v>
       </c>
@@ -1504,8 +1742,11 @@
       <c r="D11" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="E11" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>174</v>
       </c>
@@ -1522,7 +1763,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>178</v>
       </c>
@@ -1539,7 +1780,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>164</v>
       </c>
@@ -1553,7 +1794,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>192</v>
       </c>
@@ -1568,7 +1809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>195</v>
       </c>
@@ -1580,10 +1821,10 @@
       </c>
       <c r="E16">
         <f>SUM(E62:E76)</f>
-        <v>0.96</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>0</v>
       </c>
@@ -1600,7 +1841,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>69</v>
       </c>
@@ -1620,7 +1861,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>27</v>
       </c>
@@ -1634,7 +1875,7 @@
         <v>0.74</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>29</v>
       </c>
@@ -1645,7 +1886,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>226</v>
       </c>
@@ -1659,7 +1900,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>31</v>
       </c>
@@ -1670,7 +1911,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>32</v>
       </c>
@@ -1688,10 +1929,10 @@
         <v>15</v>
       </c>
       <c r="F24" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.5">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>42</v>
       </c>
@@ -1701,8 +1942,21 @@
       <c r="D25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.5">
+      <c r="F25" s="4">
+        <v>16</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="H25" s="4">
+        <v>103</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="J25" s="4"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>138</v>
       </c>
@@ -1720,13 +1974,18 @@
         <v>4</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="H26" s="4"/>
-      <c r="I26" s="4"/>
+        <v>250</v>
+      </c>
+      <c r="H26" s="8">
+        <f>10000*(BW^0.514994446*(BH^0.422014803)*0.023492833)</f>
+        <v>6926.2410142047056</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>282</v>
+      </c>
       <c r="J26" s="4"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>139</v>
       </c>
@@ -1741,17 +2000,16 @@
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="4">
-        <f>2.9*60/1000</f>
-        <v>0.17399999999999999</v>
+        <f>30.6*EXP(-0.166*age)*(60/1000)*(BW^0.75)</f>
+        <v>7.5612070026140072</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="H27" s="4"/>
       <c r="I27" s="4"/>
-      <c r="J27" s="4"/>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.5">
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>47</v>
       </c>
@@ -1765,17 +2023,16 @@
         <v>0</v>
       </c>
       <c r="F28" s="4">
-        <f>F27/(70^0.75)</f>
-        <v>7.1899474840331325E-3</v>
+        <f>F27/(BW^0.75)</f>
+        <v>0.94515087532675113</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="H28" s="4"/>
       <c r="I28" s="4"/>
-      <c r="J28" s="4"/>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.5">
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>140</v>
       </c>
@@ -1789,17 +2046,16 @@
         <v>0</v>
       </c>
       <c r="F29" s="4">
-        <f>0.1 + 0.4*F26/18</f>
-        <v>0.18888888888888888</v>
+        <f>0.1 + 0.0222*age</f>
+        <v>0.18880000000000002</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H29" s="4"/>
       <c r="I29" s="4"/>
-      <c r="J29" s="4"/>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.5">
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>141</v>
       </c>
@@ -1813,17 +2069,16 @@
         <v>0</v>
       </c>
       <c r="F30" s="4">
-        <f>0.9-0.4*F26/18</f>
-        <v>0.81111111111111112</v>
+        <f>0.9-0.0222*age</f>
+        <v>0.81120000000000003</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="H30" s="4"/>
       <c r="I30" s="4"/>
-      <c r="J30" s="4"/>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.5">
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>142</v>
       </c>
@@ -1837,7 +2092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>51</v>
       </c>
@@ -1854,7 +2109,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>52</v>
       </c>
@@ -1868,7 +2123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>53</v>
       </c>
@@ -1882,7 +2137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>54</v>
       </c>
@@ -1895,8 +2150,11 @@
       <c r="D35">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="F35" s="4" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>165</v>
       </c>
@@ -1910,14 +2168,18 @@
         <v>0</v>
       </c>
       <c r="E36" s="4">
-        <f>F28*F29</f>
-        <v>1.3581011914284805E-3</v>
-      </c>
-      <c r="F36" t="s">
+        <f>F36/(BW^0.75)</f>
+        <v>0.17844448526169063</v>
+      </c>
+      <c r="F36" s="4">
+        <f>CLp*F29</f>
+        <v>1.4275558820935248</v>
+      </c>
+      <c r="G36" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>56</v>
       </c>
@@ -1931,7 +2193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>237</v>
       </c>
@@ -1945,7 +2207,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>236</v>
       </c>
@@ -1959,7 +2221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>238</v>
       </c>
@@ -1973,7 +2235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>143</v>
       </c>
@@ -1990,7 +2252,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>144</v>
       </c>
@@ -2004,7 +2266,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>145</v>
       </c>
@@ -2018,7 +2280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>146</v>
       </c>
@@ -2035,7 +2297,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>147</v>
       </c>
@@ -2049,7 +2311,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>203</v>
       </c>
@@ -2062,12 +2324,17 @@
       <c r="D46">
         <v>0</v>
       </c>
-      <c r="E46" s="4">
-        <f>F28*F30/E75</f>
-        <v>8.3312089894352168E-2</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="E46" s="4"/>
+      <c r="F46" s="4">
+        <f>CLp*F30</f>
+        <v>6.1336511205204829</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="H46" s="4"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>148</v>
       </c>
@@ -2084,7 +2351,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>149</v>
       </c>
@@ -2098,7 +2365,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>150</v>
       </c>
@@ -2112,7 +2379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>37</v>
       </c>
@@ -2123,7 +2390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>168</v>
       </c>
@@ -2134,7 +2401,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>39</v>
       </c>
@@ -2145,7 +2412,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>184</v>
       </c>
@@ -2159,7 +2426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>160</v>
       </c>
@@ -2173,7 +2440,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>161</v>
       </c>
@@ -2184,7 +2451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>198</v>
       </c>
@@ -2198,7 +2465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>200</v>
       </c>
@@ -2212,7 +2479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>231</v>
       </c>
@@ -2229,7 +2496,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>41</v>
       </c>
@@ -2240,7 +2507,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>0</v>
       </c>
@@ -2257,7 +2524,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>79</v>
       </c>
@@ -2274,7 +2541,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>134</v>
       </c>
@@ -2291,7 +2558,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>136</v>
       </c>
@@ -2308,7 +2575,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>82</v>
       </c>
@@ -2325,7 +2592,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>89</v>
       </c>
@@ -2341,8 +2608,11 @@
       <c r="F66" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="G66" s="4" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>90</v>
       </c>
@@ -2355,14 +2625,18 @@
       <c r="D67">
         <v>1</v>
       </c>
-      <c r="E67">
-        <v>0.03</v>
+      <c r="E67" s="4">
+        <v>2.5999999999999999E-2</v>
       </c>
       <c r="F67" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="G67" s="4">
+        <f>E67*BW</f>
+        <v>0.41599999999999998</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>91</v>
       </c>
@@ -2375,14 +2649,19 @@
       <c r="D68">
         <v>1</v>
       </c>
-      <c r="E68">
-        <v>4.0000000000000001E-3</v>
+      <c r="E68" s="4">
+        <f>((4.214*BW^0.823)+(4.456*BW^0.795))/(BW*1000)</f>
+        <v>5.1037420752262702E-3</v>
       </c>
       <c r="F68" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="G68" s="4">
+        <f>E68*BW</f>
+        <v>8.1659873203620323E-2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>92</v>
       </c>
@@ -2399,12 +2678,12 @@
         <v>219</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>93</v>
       </c>
       <c r="B70" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C70" t="s">
         <v>186</v>
@@ -2412,14 +2691,19 @@
       <c r="D70">
         <v>1</v>
       </c>
-      <c r="E70">
-        <v>3.5999999999999997E-2</v>
+      <c r="E70" s="4">
+        <f>(((-0.005309*age+1.008*BW^0.493+BH^0.3765-7.952)+( 0.002331*age+0.1253*BW^0.8477+BH^0.3821-4.725))/(2*BW))-E67-E68</f>
+        <v>9.9581643578766893E-2</v>
       </c>
       <c r="F70" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.5">
+        <v>259</v>
+      </c>
+      <c r="G70" s="4">
+        <f>E70*BW</f>
+        <v>1.5933062972602703</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>94</v>
       </c>
@@ -2436,7 +2720,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>95</v>
       </c>
@@ -2453,7 +2737,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>96</v>
       </c>
@@ -2470,7 +2754,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="74" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>97</v>
       </c>
@@ -2486,13 +2770,16 @@
       <c r="F74" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="J74" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
         <v>98</v>
       </c>
       <c r="B75" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C75" t="s">
         <v>186</v>
@@ -2500,19 +2787,28 @@
       <c r="D75">
         <v>1</v>
       </c>
-      <c r="E75">
+      <c r="E75" s="4">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="F75" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="F75" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="G75" s="4">
+        <f>E75*BW</f>
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="J75" s="9"/>
+      <c r="K75" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="L75" s="11"/>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>151</v>
       </c>
       <c r="B76" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C76" t="s">
         <v>186</v>
@@ -2520,14 +2816,26 @@
       <c r="D76">
         <v>1</v>
       </c>
-      <c r="E76">
-        <v>0.82</v>
-      </c>
-      <c r="F76" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="E76" s="4">
+        <f>1-SUM(E67:E75)</f>
+        <v>0.79931461434600681</v>
+      </c>
+      <c r="F76" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="G76" s="7">
+        <f>E76*BW</f>
+        <v>12.789033829536109</v>
+      </c>
+      <c r="J76" s="12"/>
+      <c r="K76" s="13" t="s">
+        <v>276</v>
+      </c>
+      <c r="L76" s="14" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>104</v>
       </c>
@@ -2543,8 +2851,26 @@
       <c r="F77" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="G77" s="7">
+        <f>(360*(BW^0.74))/24</f>
+        <v>116.71859368947428</v>
+      </c>
+      <c r="H77" t="s">
+        <v>274</v>
+      </c>
+      <c r="J77" s="15" t="s">
+        <v>277</v>
+      </c>
+      <c r="K77" s="13">
+        <f>0.00119*BW-0.0004302</f>
+        <v>1.8609800000000003E-2</v>
+      </c>
+      <c r="L77" s="14">
+        <f>0.03*K77</f>
+        <v>5.5829400000000009E-4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>105</v>
       </c>
@@ -2557,14 +2883,30 @@
       <c r="D78">
         <v>0</v>
       </c>
-      <c r="E78">
-        <v>0.24</v>
+      <c r="E78" s="4" cm="1">
+        <f t="array" ref="E78">G78/Qct</f>
+        <v>3.278997697815081E-3</v>
       </c>
       <c r="F78" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="G78" s="7">
+        <f>0.92*G67</f>
+        <v>0.38272</v>
+      </c>
+      <c r="J78" s="15" t="s">
+        <v>278</v>
+      </c>
+      <c r="K78" s="13">
+        <f>0.0000001017*((BH^0.6862*BW^0.3561*242.7+BH^0.664*BW^0.3851*242.7)/2)^1.42</f>
+        <v>9.0660865954799885E-2</v>
+      </c>
+      <c r="L78" s="14">
+        <f>0.845*K78</f>
+        <v>7.6608431731805898E-2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>106</v>
       </c>
@@ -2577,14 +2919,29 @@
       <c r="D79">
         <v>0</v>
       </c>
-      <c r="E79">
-        <v>0.15</v>
+      <c r="E79" s="4">
+        <v>0.18</v>
       </c>
       <c r="F79" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="G79" s="7">
+        <f>E79*Qct</f>
+        <v>21.009346864105368</v>
+      </c>
+      <c r="J79" s="15" t="s">
+        <v>279</v>
+      </c>
+      <c r="K79" s="13">
+        <f>((6.78*(surface/10000)^1.629-0.001492*age+3.58)+(0.2598*BW+0.1206*BH-0.0043*age-11.1)/1.04)/2</f>
+        <v>6.2763645433826127</v>
+      </c>
+      <c r="L79" s="14">
+        <f>0.03*K79</f>
+        <v>0.18829093630147836</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>107</v>
       </c>
@@ -2597,14 +2954,33 @@
       <c r="D80">
         <v>0</v>
       </c>
-      <c r="E80">
-        <v>0.36</v>
+      <c r="E80" s="5">
+        <f>1-SUM(E78:E79,E85:E86)</f>
+        <v>0.76216599738664981</v>
       </c>
       <c r="F80" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.5">
+        <v>259</v>
+      </c>
+      <c r="G80" s="7">
+        <f>E80*Qct</f>
+        <v>88.958943372905296</v>
+      </c>
+      <c r="H80" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="J80" s="15" t="s">
+        <v>280</v>
+      </c>
+      <c r="K80" s="13">
+        <f>SUM(K77:K79)</f>
+        <v>6.3856352093374129</v>
+      </c>
+      <c r="L80" s="14">
+        <f>SUM(L77:L79)</f>
+        <v>0.26545766203328425</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
         <v>108</v>
       </c>
@@ -2620,8 +2996,17 @@
       <c r="F81" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.5">
+      <c r="J81" s="9"/>
+      <c r="K81" s="16">
+        <f>Vtf/K80</f>
+        <v>2.002781776640687</v>
+      </c>
+      <c r="L81" s="11">
+        <f>K81*L80</f>
+        <v>0.53165376798990405</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>109</v>
       </c>
@@ -2637,8 +3022,16 @@
       <c r="F82" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.5">
+      <c r="K82" s="17" t="s">
+        <v>283</v>
+      </c>
+      <c r="L82" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="M82" s="4"/>
+      <c r="N82" s="4"/>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>110</v>
       </c>
@@ -2654,8 +3047,16 @@
       <c r="F83" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.5">
+      <c r="K83" s="17" t="s">
+        <v>284</v>
+      </c>
+      <c r="L83" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="M83" s="4"/>
+      <c r="N83" s="4"/>
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>111</v>
       </c>
@@ -2672,12 +3073,12 @@
         <v>223</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>112</v>
       </c>
       <c r="B85" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C85" t="s">
         <v>185</v>
@@ -2688,17 +3089,21 @@
       <c r="E85" s="6">
         <v>0.05</v>
       </c>
-      <c r="F85" t="s">
-        <v>262</v>
-      </c>
-      <c r="G85" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="H85" s="6"/>
+      <c r="F85" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="G85" s="7">
+        <f>E85*Qct</f>
+        <v>5.8359296844737143</v>
+      </c>
+      <c r="H85" s="6" t="s">
+        <v>261</v>
+      </c>
       <c r="I85" s="6"/>
       <c r="J85" s="6"/>
-    </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.5">
+      <c r="K85" s="6"/>
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>153</v>
       </c>
@@ -2711,19 +3116,19 @@
       <c r="D86">
         <v>0</v>
       </c>
-      <c r="E86" s="5">
-        <f>1-SUM(E78:E85)</f>
-        <v>0.19999999999999996</v>
-      </c>
-      <c r="F86" t="s">
-        <v>225</v>
-      </c>
-      <c r="G86" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="H86" s="5"/>
-    </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.5">
+      <c r="E86" s="4">
+        <f>G86/Qct</f>
+        <v>4.5550049155351395E-3</v>
+      </c>
+      <c r="F86" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="G86" s="7">
+        <f>L81</f>
+        <v>0.53165376798990405</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>121</v>
       </c>
@@ -2737,7 +3142,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>122</v>
       </c>
@@ -2750,8 +3155,12 @@
       <c r="F88" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.5">
+      <c r="G88" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="H88" s="4"/>
+    </row>
+    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>123</v>
       </c>
@@ -2761,14 +3170,18 @@
       <c r="D89">
         <v>1</v>
       </c>
-      <c r="E89">
-        <v>0.98</v>
+      <c r="E89" s="7">
+        <f>G89*1.333</f>
+        <v>1.3063399999999998</v>
       </c>
       <c r="F89" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.5">
+      <c r="G89">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>124</v>
       </c>
@@ -2778,14 +3191,18 @@
       <c r="D90">
         <v>1</v>
       </c>
-      <c r="E90">
-        <v>4.16</v>
+      <c r="E90" s="7">
+        <f t="shared" ref="E90:E91" si="0">G90*1.333</f>
+        <v>5.54528</v>
       </c>
       <c r="F90" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.5">
+      <c r="G90">
+        <v>4.16</v>
+      </c>
+    </row>
+    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>125</v>
       </c>
@@ -2795,14 +3212,18 @@
       <c r="D91">
         <v>1</v>
       </c>
-      <c r="E91">
+      <c r="E91" s="7">
+        <f t="shared" si="0"/>
+        <v>1.10639</v>
+      </c>
+      <c r="F91" t="s">
+        <v>259</v>
+      </c>
+      <c r="G91">
         <v>0.83</v>
       </c>
-      <c r="F91" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.5">
+    </row>
+    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>126</v>
       </c>
@@ -2812,11 +3233,12 @@
       <c r="D92">
         <v>1</v>
       </c>
+      <c r="E92" s="18"/>
       <c r="F92" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>127</v>
       </c>
@@ -2826,11 +3248,12 @@
       <c r="D93">
         <v>1</v>
       </c>
+      <c r="E93" s="18"/>
       <c r="F93" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>128</v>
       </c>
@@ -2840,11 +3263,12 @@
       <c r="D94">
         <v>1</v>
       </c>
+      <c r="E94" s="18"/>
       <c r="F94" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>129</v>
       </c>
@@ -2854,11 +3278,12 @@
       <c r="D95">
         <v>1</v>
       </c>
+      <c r="E95" s="18"/>
       <c r="F95" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>130</v>
       </c>
@@ -2868,14 +3293,18 @@
       <c r="D96">
         <v>1</v>
       </c>
-      <c r="E96">
+      <c r="E96" s="7">
+        <f t="shared" ref="E96:E97" si="1">G96*1.333</f>
+        <v>1333</v>
+      </c>
+      <c r="F96" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="G96">
         <v>1000</v>
       </c>
-      <c r="F96" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.5">
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>156</v>
       </c>
@@ -2885,14 +3314,18 @@
       <c r="D97">
         <v>1</v>
       </c>
-      <c r="E97">
+      <c r="E97" s="7">
+        <f t="shared" si="1"/>
+        <v>0.83979000000000004</v>
+      </c>
+      <c r="F97" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="G97">
         <v>0.63</v>
       </c>
-      <c r="F97" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.5">
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>0</v>
       </c>
@@ -2909,7 +3342,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>34</v>
       </c>
@@ -2917,7 +3350,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>0</v>
       </c>
@@ -2932,7 +3365,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>73</v>
       </c>
@@ -2940,7 +3373,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>75</v>
       </c>
@@ -2948,7 +3381,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>77</v>
       </c>
@@ -2988,21 +3421,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2530FCFD-82CD-436F-B981-3C7AACA19280}">
   <dimension ref="A1:J105"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.29296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="51" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.41015625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.1171875" customWidth="1"/>
-    <col min="5" max="5" width="22.29296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.29296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.41015625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.5859375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" customWidth="1"/>
+    <col min="5" max="5" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.5859375" customWidth="1"/>
+    <col min="10" max="10" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3022,7 +3455,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -3033,7 +3466,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -3041,7 +3474,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -3049,7 +3482,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
@@ -3060,13 +3493,13 @@
         <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F5" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -3083,7 +3516,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
@@ -3097,7 +3530,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>20</v>
       </c>
@@ -3114,7 +3547,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>245</v>
       </c>
@@ -3129,7 +3562,7 @@
       </c>
       <c r="E9" s="2"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>132</v>
       </c>
@@ -3143,7 +3576,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>133</v>
       </c>
@@ -3157,7 +3590,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>174</v>
       </c>
@@ -3174,7 +3607,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>178</v>
       </c>
@@ -3191,7 +3624,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>164</v>
       </c>
@@ -3205,7 +3638,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>192</v>
       </c>
@@ -3220,7 +3653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>195</v>
       </c>
@@ -3232,10 +3665,10 @@
       </c>
       <c r="E16">
         <f>SUM(E62:E76)</f>
-        <v>0.96</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.5">
+        <v>0.95599999999999996</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>0</v>
       </c>
@@ -3252,7 +3685,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>69</v>
       </c>
@@ -3272,7 +3705,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>27</v>
       </c>
@@ -3286,7 +3719,7 @@
         <v>0.74</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>29</v>
       </c>
@@ -3297,7 +3730,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>226</v>
       </c>
@@ -3311,7 +3744,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>31</v>
       </c>
@@ -3322,7 +3755,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>32</v>
       </c>
@@ -3340,10 +3773,10 @@
         <v>15</v>
       </c>
       <c r="F24" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.5">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>42</v>
       </c>
@@ -3353,8 +3786,14 @@
       <c r="D25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.5">
+      <c r="F25" s="4">
+        <v>25</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>138</v>
       </c>
@@ -3372,13 +3811,12 @@
         <v>8</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H26" s="4"/>
       <c r="I26" s="4"/>
-      <c r="J26" s="4"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.5">
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>139</v>
       </c>
@@ -3393,17 +3831,16 @@
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="4">
-        <f>2.9*60/1000</f>
-        <v>0.17399999999999999</v>
+        <f>30.6*EXP(-0.166*F$26)*(60/1000)*(F25^0.75)</f>
+        <v>5.439821026844017</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="H27" s="4"/>
       <c r="I27" s="4"/>
-      <c r="J27" s="4"/>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.5">
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>47</v>
       </c>
@@ -3417,17 +3854,16 @@
         <v>0</v>
       </c>
       <c r="F28" s="4">
-        <f>F27/(70^0.75)</f>
-        <v>7.1899474840331325E-3</v>
+        <f>F27/(F25^0.75)</f>
+        <v>0.48655238405823736</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="H28" s="4"/>
       <c r="I28" s="4"/>
-      <c r="J28" s="4"/>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.5">
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>140</v>
       </c>
@@ -3441,17 +3877,16 @@
         <v>0</v>
       </c>
       <c r="F29" s="4">
-        <f>0.1 + 0.4*F26/18</f>
-        <v>0.27777777777777779</v>
+        <f>0.1 + 0.0222*F26</f>
+        <v>0.27760000000000001</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H29" s="4"/>
       <c r="I29" s="4"/>
-      <c r="J29" s="4"/>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.5">
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>141</v>
       </c>
@@ -3465,17 +3900,16 @@
         <v>0</v>
       </c>
       <c r="F30" s="4">
-        <f>0.9-0.4*F26/18</f>
-        <v>0.72222222222222221</v>
+        <f>0.9-0.0222*F26</f>
+        <v>0.72240000000000004</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="H30" s="4"/>
       <c r="I30" s="4"/>
-      <c r="J30" s="4"/>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.5">
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>142</v>
       </c>
@@ -3489,7 +3923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>51</v>
       </c>
@@ -3506,7 +3940,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>52</v>
       </c>
@@ -3520,7 +3954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>53</v>
       </c>
@@ -3534,7 +3968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>54</v>
       </c>
@@ -3548,7 +3982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>165</v>
       </c>
@@ -3563,13 +3997,13 @@
       </c>
       <c r="E36" s="4">
         <f>F28*F29</f>
-        <v>1.997207634453648E-3</v>
+        <v>0.13506694181456669</v>
       </c>
       <c r="F36" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>56</v>
       </c>
@@ -3582,8 +4016,15 @@
       <c r="D37">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="F37">
+        <f>E36*F$25^0.75</f>
+        <v>1.5100943170518992</v>
+      </c>
+      <c r="G37" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>237</v>
       </c>
@@ -3597,7 +4038,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>236</v>
       </c>
@@ -3611,7 +4052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>238</v>
       </c>
@@ -3625,7 +4066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>143</v>
       </c>
@@ -3642,7 +4083,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>144</v>
       </c>
@@ -3656,7 +4097,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>145</v>
       </c>
@@ -3670,7 +4111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>146</v>
       </c>
@@ -3687,7 +4128,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>147</v>
       </c>
@@ -3701,7 +4142,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>203</v>
       </c>
@@ -3714,12 +4155,16 @@
       <c r="D46">
         <v>0</v>
       </c>
-      <c r="E46" s="4">
-        <f>F28*F30/E75</f>
-        <v>7.4181997851135495E-2</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="E46" s="4"/>
+      <c r="F46">
+        <f>F27*F30</f>
+        <v>3.929726709792118</v>
+      </c>
+      <c r="G46" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>148</v>
       </c>
@@ -3736,7 +4181,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>149</v>
       </c>
@@ -3750,7 +4195,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>150</v>
       </c>
@@ -3764,7 +4209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>37</v>
       </c>
@@ -3775,7 +4220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>168</v>
       </c>
@@ -3786,7 +4231,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>39</v>
       </c>
@@ -3797,7 +4242,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>184</v>
       </c>
@@ -3811,7 +4256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>160</v>
       </c>
@@ -3825,7 +4270,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>161</v>
       </c>
@@ -3836,7 +4281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>198</v>
       </c>
@@ -3850,7 +4295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>200</v>
       </c>
@@ -3864,7 +4309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>231</v>
       </c>
@@ -3881,7 +4326,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>41</v>
       </c>
@@ -3892,7 +4337,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>0</v>
       </c>
@@ -3909,7 +4354,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>79</v>
       </c>
@@ -3926,7 +4371,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>134</v>
       </c>
@@ -3943,7 +4388,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>136</v>
       </c>
@@ -3960,7 +4405,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>82</v>
       </c>
@@ -3977,7 +4422,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>89</v>
       </c>
@@ -3994,7 +4439,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>90</v>
       </c>
@@ -4008,13 +4453,13 @@
         <v>1</v>
       </c>
       <c r="E67">
-        <v>0.03</v>
+        <v>2.5999999999999999E-2</v>
       </c>
       <c r="F67" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>91</v>
       </c>
@@ -4034,7 +4479,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>92</v>
       </c>
@@ -4051,12 +4496,12 @@
         <v>219</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>93</v>
       </c>
       <c r="B70" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C70" t="s">
         <v>186</v>
@@ -4068,10 +4513,10 @@
         <v>3.5999999999999997E-2</v>
       </c>
       <c r="F70" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.5">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>94</v>
       </c>
@@ -4088,7 +4533,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>95</v>
       </c>
@@ -4105,7 +4550,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>96</v>
       </c>
@@ -4122,7 +4567,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>97</v>
       </c>
@@ -4139,12 +4584,12 @@
         <v>223</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>98</v>
       </c>
       <c r="B75" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C75" t="s">
         <v>186</v>
@@ -4159,12 +4604,12 @@
         <v>224</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>151</v>
       </c>
       <c r="B76" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C76" t="s">
         <v>186</v>
@@ -4179,7 +4624,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>104</v>
       </c>
@@ -4196,7 +4641,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>105</v>
       </c>
@@ -4216,7 +4661,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>106</v>
       </c>
@@ -4236,7 +4681,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>107</v>
       </c>
@@ -4253,10 +4698,10 @@
         <v>0.36</v>
       </c>
       <c r="F80" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.5">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>108</v>
       </c>
@@ -4273,7 +4718,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>109</v>
       </c>
@@ -4290,7 +4735,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>110</v>
       </c>
@@ -4307,7 +4752,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>111</v>
       </c>
@@ -4324,12 +4769,12 @@
         <v>223</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>112</v>
       </c>
       <c r="B85" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C85" t="s">
         <v>185</v>
@@ -4341,16 +4786,16 @@
         <v>0.05</v>
       </c>
       <c r="F85" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="G85" s="6" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="H85" s="6"/>
       <c r="I85" s="6"/>
       <c r="J85" s="6"/>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>153</v>
       </c>
@@ -4371,11 +4816,11 @@
         <v>225</v>
       </c>
       <c r="G86" s="5" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H86" s="5"/>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>121</v>
       </c>
@@ -4389,7 +4834,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>122</v>
       </c>
@@ -4403,7 +4848,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>123</v>
       </c>
@@ -4420,7 +4865,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>124</v>
       </c>
@@ -4437,7 +4882,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>125</v>
       </c>
@@ -4451,10 +4896,10 @@
         <v>0.83</v>
       </c>
       <c r="F91" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.5">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>126</v>
       </c>
@@ -4468,7 +4913,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>127</v>
       </c>
@@ -4482,7 +4927,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>128</v>
       </c>
@@ -4496,7 +4941,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>129</v>
       </c>
@@ -4510,7 +4955,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>130</v>
       </c>
@@ -4527,7 +4972,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>156</v>
       </c>
@@ -4544,7 +4989,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>0</v>
       </c>
@@ -4561,7 +5006,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>34</v>
       </c>
@@ -4569,7 +5014,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>0</v>
       </c>
@@ -4584,7 +5029,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>73</v>
       </c>
@@ -4592,7 +5037,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>75</v>
       </c>
@@ -4600,7 +5045,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>77</v>
       </c>
@@ -4638,51 +5083,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Source xmlns="http://schemas.microsoft.com/sharepoint/v3/fields" xsi:nil="true"/>
-    <Language xmlns="http://schemas.microsoft.com/sharepoint/v3">English</Language>
-    <j747ac98061d40f0aa7bd47e1db5675d xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </j747ac98061d40f0aa7bd47e1db5675d>
-    <External_x0020_Contributor xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
-    <TaxKeywordTaxHTField xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </TaxKeywordTaxHTField>
-    <Record xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">Shared</Record>
-    <Rights xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
-    <Document_x0020_Creation_x0020_Date xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">2020-10-14T20:30:29+00:00</Document_x0020_Creation_x0020_Date>
-    <EPA_x0020_Office xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
-    <CategoryDescription xmlns="http://schemas.microsoft.com/sharepoint.v3" xsi:nil="true"/>
-    <Identifier xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
-    <_Coverage xmlns="http://schemas.microsoft.com/sharepoint/v3/fields" xsi:nil="true"/>
-    <Creator xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Creator>
-    <EPA_x0020_Related_x0020_Documents xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
-    <EPA_x0020_Contributor xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </EPA_x0020_Contributor>
-    <TaxCatchAll xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
-    <e3f09c3df709400db2417a7161762d62 xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </e3f09c3df709400db2417a7161762d62>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2ba80736-48fa-4d73-aaff-bacaeeed013a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="29f62856-1543-49d4-a736-4569d363f533" ContentTypeId="0x0101" PreviousValue="false"/>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C107526348C97345843FB1F7E3F5FF14" ma:contentTypeVersion="20" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1f5efa0b4590ceb4068c523eef838cbf">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xmlns:ns3="http://schemas.microsoft.com/sharepoint.v3" xmlns:ns4="http://schemas.microsoft.com/sharepoint/v3/fields" xmlns:ns5="2ba80736-48fa-4d73-aaff-bacaeeed013a" xmlns:ns6="41d9f072-86bf-4c63-b117-debf50ff4701" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9d32b47d5805bf9e4ccfb00021215c68" ns1:_="" ns2:_="" ns3:_="" ns4:_="" ns5:_="" ns6:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -5155,36 +5569,68 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="29f62856-1543-49d4-a736-4569d363f533" ContentTypeId="0x0101" PreviousValue="false"/>
-</file>
-
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_Source xmlns="http://schemas.microsoft.com/sharepoint/v3/fields" xsi:nil="true"/>
+    <Language xmlns="http://schemas.microsoft.com/sharepoint/v3">English</Language>
+    <j747ac98061d40f0aa7bd47e1db5675d xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </j747ac98061d40f0aa7bd47e1db5675d>
+    <External_x0020_Contributor xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
+    <TaxKeywordTaxHTField xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </TaxKeywordTaxHTField>
+    <Record xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">Shared</Record>
+    <Rights xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
+    <Document_x0020_Creation_x0020_Date xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">2020-10-14T20:30:29+00:00</Document_x0020_Creation_x0020_Date>
+    <EPA_x0020_Office xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
+    <CategoryDescription xmlns="http://schemas.microsoft.com/sharepoint.v3" xsi:nil="true"/>
+    <Identifier xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
+    <_Coverage xmlns="http://schemas.microsoft.com/sharepoint/v3/fields" xsi:nil="true"/>
+    <Creator xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Creator>
+    <EPA_x0020_Related_x0020_Documents xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
+    <EPA_x0020_Contributor xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </EPA_x0020_Contributor>
+    <TaxCatchAll xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
+    <e3f09c3df709400db2417a7161762d62 xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </e3f09c3df709400db2417a7161762d62>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2ba80736-48fa-4d73-aaff-bacaeeed013a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA939294-F21F-45CD-81A6-3A616888DAC5}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4DC26B68-A11F-428F-9051-23DC6334A810}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/fields"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4"/>
-    <ds:schemaRef ds:uri="93237db7-bebb-43bb-9414-bc3313990c09"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint.v3"/>
-    <ds:schemaRef ds:uri="2ba80736-48fa-4d73-aaff-bacaeeed013a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C4A2D8C-C5B5-46A0-8FC1-3730CC1A83D7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{90A172F1-773B-43BF-8B86-8CD1537A96AE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5207,18 +5653,17 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C4A2D8C-C5B5-46A0-8FC1-3730CC1A83D7}">
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA939294-F21F-45CD-81A6-3A616888DAC5}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4DC26B68-A11F-428F-9051-23DC6334A810}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/fields"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4"/>
+    <ds:schemaRef ds:uri="93237db7-bebb-43bb-9414-bc3313990c09"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint.v3"/>
+    <ds:schemaRef ds:uri="2ba80736-48fa-4d73-aaff-bacaeeed013a"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Inputs/F_template_parameters_Model.xlsx
+++ b/Inputs/F_template_parameters_Model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usepa-my.sharepoint.com/personal/schlosser_paul_epa_gov/Documents/mcsim-5.6.5/PBPK_Model_Template_Mod/Inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="257" documentId="8_{7F8D94C6-EC2B-4A79-A22A-AD1B7807B962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9BAEC706-8C59-4BC2-9C2F-BEF881BFFAC2}"/>
+  <xr:revisionPtr revIDLastSave="295" documentId="8_{7F8D94C6-EC2B-4A79-A22A-AD1B7807B962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0CD96151-D1AD-4DB3-9455-7E599C57FEA7}"/>
   <bookViews>
-    <workbookView xWindow="-23040" yWindow="45" windowWidth="25410" windowHeight="14640" xr2:uid="{089E7848-11EB-427A-89EA-83825F220BA0}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="24600" windowHeight="13290" xr2:uid="{089E7848-11EB-427A-89EA-83825F220BA0}"/>
   </bookViews>
   <sheets>
     <sheet name="Human4yo" sheetId="9" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="290">
   <si>
     <t>Code</t>
   </si>
@@ -874,9 +874,6 @@
     <t>Total plasma CL (L/h ~ kg/h; Jean 2016)</t>
   </si>
   <si>
-    <t>Tota urinary CL (L/h) V</t>
-  </si>
-  <si>
     <t>&lt;= Total bone CL (L/h)</t>
   </si>
   <si>
@@ -935,6 +932,12 @@
   </si>
   <si>
     <t>Below was copied, with limited translation, from the Jean et al. spreadsheet</t>
+  </si>
+  <si>
+    <t>used for kidney</t>
+  </si>
+  <si>
+    <t>Tota urinary [kidney] CL (L/h) from plasma; multiply by 1.333 to get CL from blood</t>
   </si>
 </sst>
 </file>
@@ -1091,7 +1094,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1127,6 +1130,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1263,10 +1267,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1709,7 +1709,7 @@
         <v>2</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -1952,7 +1952,7 @@
         <v>103</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="J25" s="4"/>
     </row>
@@ -1981,7 +1981,7 @@
         <v>6926.2410142047056</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="J26" s="4"/>
     </row>
@@ -2045,6 +2045,9 @@
       <c r="D29">
         <v>0</v>
       </c>
+      <c r="E29">
+        <v>100</v>
+      </c>
       <c r="F29" s="4">
         <f>0.1 + 0.0222*age</f>
         <v>0.18880000000000002</v>
@@ -2091,6 +2094,14 @@
       <c r="D31">
         <v>0</v>
       </c>
+      <c r="F31" s="4">
+        <f>CLp*F$30</f>
+        <v>6.1336511205204829</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="H31" s="4"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
@@ -2109,7 +2120,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>52</v>
       </c>
@@ -2123,7 +2134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>53</v>
       </c>
@@ -2137,7 +2148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>54</v>
       </c>
@@ -2150,11 +2161,12 @@
       <c r="D35">
         <v>0</v>
       </c>
-      <c r="F35" s="4" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>165</v>
       </c>
@@ -2167,174 +2179,172 @@
       <c r="D36">
         <v>0</v>
       </c>
-      <c r="E36" s="4">
-        <f>F36/(BW^0.75)</f>
-        <v>0.17844448526169063</v>
-      </c>
-      <c r="F36" s="4">
+      <c r="G36" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B37" t="s">
+        <v>167</v>
+      </c>
+      <c r="C37" t="s">
+        <v>190</v>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B38" t="s">
+        <v>57</v>
+      </c>
+      <c r="C38" t="s">
+        <v>46</v>
+      </c>
+      <c r="D38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B39" t="s">
+        <v>58</v>
+      </c>
+      <c r="C39" t="s">
+        <v>59</v>
+      </c>
+      <c r="D39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B40" t="s">
+        <v>60</v>
+      </c>
+      <c r="C40" t="s">
+        <v>36</v>
+      </c>
+      <c r="D40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B41" t="s">
+        <v>61</v>
+      </c>
+      <c r="C41" t="s">
+        <v>189</v>
+      </c>
+      <c r="D41">
+        <v>0</v>
+      </c>
+      <c r="F41" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B42" t="s">
+        <v>62</v>
+      </c>
+      <c r="C42" t="s">
+        <v>46</v>
+      </c>
+      <c r="D42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B43" t="s">
+        <v>63</v>
+      </c>
+      <c r="C43" t="s">
+        <v>244</v>
+      </c>
+      <c r="D43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B44" t="s">
+        <v>64</v>
+      </c>
+      <c r="C44" t="s">
+        <v>189</v>
+      </c>
+      <c r="D44">
+        <v>0</v>
+      </c>
+      <c r="F44" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B45" t="s">
+        <v>65</v>
+      </c>
+      <c r="C45" t="s">
+        <v>46</v>
+      </c>
+      <c r="D45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B46" t="s">
+        <v>204</v>
+      </c>
+      <c r="C46" t="s">
+        <v>244</v>
+      </c>
+      <c r="D46">
+        <v>0</v>
+      </c>
+      <c r="E46" s="4">
+        <f>F46*1.333/(E75*(BW^0.75))</f>
+        <v>46.606293058664804</v>
+      </c>
+      <c r="F46" s="4">
         <f>CLp*F29</f>
         <v>1.4275558820935248</v>
       </c>
-      <c r="G36" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B37" t="s">
-        <v>167</v>
-      </c>
-      <c r="C37" t="s">
-        <v>190</v>
-      </c>
-      <c r="D37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="B38" t="s">
-        <v>57</v>
-      </c>
-      <c r="C38" t="s">
-        <v>46</v>
-      </c>
-      <c r="D38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="B39" t="s">
-        <v>58</v>
-      </c>
-      <c r="C39" t="s">
-        <v>59</v>
-      </c>
-      <c r="D39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="B40" t="s">
-        <v>60</v>
-      </c>
-      <c r="C40" t="s">
-        <v>36</v>
-      </c>
-      <c r="D40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="B41" t="s">
-        <v>61</v>
-      </c>
-      <c r="C41" t="s">
-        <v>189</v>
-      </c>
-      <c r="D41">
-        <v>0</v>
-      </c>
-      <c r="F41" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B42" t="s">
-        <v>62</v>
-      </c>
-      <c r="C42" t="s">
-        <v>46</v>
-      </c>
-      <c r="D42">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="B43" t="s">
-        <v>63</v>
-      </c>
-      <c r="C43" t="s">
-        <v>244</v>
-      </c>
-      <c r="D43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="B44" t="s">
-        <v>64</v>
-      </c>
-      <c r="C44" t="s">
-        <v>189</v>
-      </c>
-      <c r="D44">
-        <v>0</v>
-      </c>
-      <c r="F44" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="B45" t="s">
-        <v>65</v>
-      </c>
-      <c r="C45" t="s">
-        <v>46</v>
-      </c>
-      <c r="D45">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="B46" t="s">
-        <v>204</v>
-      </c>
-      <c r="C46" t="s">
-        <v>244</v>
-      </c>
-      <c r="D46">
-        <v>0</v>
-      </c>
-      <c r="E46" s="4"/>
-      <c r="F46" s="4">
-        <f>CLp*F30</f>
-        <v>6.1336511205204829</v>
-      </c>
       <c r="G46" s="4" t="s">
-        <v>269</v>
+        <v>289</v>
       </c>
       <c r="H46" s="4"/>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="K46" s="4"/>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>148</v>
       </c>
@@ -2351,7 +2361,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>149</v>
       </c>
@@ -2609,7 +2619,7 @@
         <v>216</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
@@ -2649,16 +2659,8 @@
       <c r="D68">
         <v>1</v>
       </c>
-      <c r="E68" s="4">
-        <f>((4.214*BW^0.823)+(4.456*BW^0.795))/(BW*1000)</f>
-        <v>5.1037420752262702E-3</v>
-      </c>
       <c r="F68" t="s">
         <v>218</v>
-      </c>
-      <c r="G68" s="4">
-        <f>E68*BW</f>
-        <v>8.1659873203620323E-2</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
@@ -2692,7 +2694,7 @@
         <v>1</v>
       </c>
       <c r="E70" s="4">
-        <f>(((-0.005309*age+1.008*BW^0.493+BH^0.3765-7.952)+( 0.002331*age+0.1253*BW^0.8477+BH^0.3821-4.725))/(2*BW))-E67-E68</f>
+        <f>(((-0.005309*age+1.008*BW^0.493+BH^0.3765-7.952)+( 0.002331*age+0.1253*BW^0.8477+BH^0.3821-4.725))/(2*BW))-E67-E75</f>
         <v>9.9581643578766893E-2</v>
       </c>
       <c r="F70" t="s">
@@ -2767,11 +2769,18 @@
       <c r="D74">
         <v>1</v>
       </c>
-      <c r="F74" t="s">
-        <v>223</v>
+      <c r="E74" s="4">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="G74" s="4">
+        <f>E74*BW</f>
+        <v>1.1200000000000001</v>
       </c>
       <c r="J74" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="75" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2788,18 +2797,19 @@
         <v>1</v>
       </c>
       <c r="E75" s="4">
-        <v>7.0000000000000007E-2</v>
+        <f>((4.214*BW^0.823)+(4.456*BW^0.795))/(BW*1000)</f>
+        <v>5.1037420752262702E-3</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>260</v>
+        <v>288</v>
       </c>
       <c r="G75" s="4">
         <f>E75*BW</f>
-        <v>1.1200000000000001</v>
+        <v>8.1659873203620323E-2</v>
       </c>
       <c r="J75" s="9"/>
       <c r="K75" s="10" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L75" s="11"/>
     </row>
@@ -2821,7 +2831,7 @@
         <v>0.79931461434600681</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G76" s="7">
         <f>E76*BW</f>
@@ -2829,10 +2839,10 @@
       </c>
       <c r="J76" s="12"/>
       <c r="K76" s="13" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="L76" s="14" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
@@ -2856,10 +2866,10 @@
         <v>116.71859368947428</v>
       </c>
       <c r="H77" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="J77" s="15" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="K77" s="13">
         <f>0.00119*BW-0.0004302</f>
@@ -2895,7 +2905,7 @@
         <v>0.38272</v>
       </c>
       <c r="J78" s="15" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="K78" s="13">
         <f>0.0000001017*((BH^0.6862*BW^0.3561*242.7+BH^0.664*BW^0.3851*242.7)/2)^1.42</f>
@@ -2919,18 +2929,11 @@
       <c r="D79">
         <v>0</v>
       </c>
-      <c r="E79" s="4">
-        <v>0.18</v>
-      </c>
       <c r="F79" t="s">
         <v>218</v>
       </c>
-      <c r="G79" s="7">
-        <f>E79*Qct</f>
-        <v>21.009346864105368</v>
-      </c>
       <c r="J79" s="15" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="K79" s="13">
         <f>((6.78*(surface/10000)^1.629-0.001492*age+3.58)+(0.2598*BW+0.1206*BH-0.0043*age-11.1)/1.04)/2</f>
@@ -2955,7 +2958,7 @@
         <v>0</v>
       </c>
       <c r="E80" s="5">
-        <f>1-SUM(E78:E79,E85:E86)</f>
+        <f>1-SUM(E78,E84:E86)</f>
         <v>0.76216599738664981</v>
       </c>
       <c r="F80" t="s">
@@ -2969,7 +2972,7 @@
         <v>256</v>
       </c>
       <c r="J80" s="15" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="K80" s="13">
         <f>SUM(K77:K79)</f>
@@ -3023,10 +3026,10 @@
         <v>221</v>
       </c>
       <c r="K82" s="17" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L82" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="M82" s="4"/>
       <c r="N82" s="4"/>
@@ -3048,10 +3051,10 @@
         <v>222</v>
       </c>
       <c r="K83" s="17" t="s">
+        <v>283</v>
+      </c>
+      <c r="L83" s="4" t="s">
         <v>284</v>
-      </c>
-      <c r="L83" s="4" t="s">
-        <v>285</v>
       </c>
       <c r="M83" s="4"/>
       <c r="N83" s="4"/>
@@ -3069,9 +3072,22 @@
       <c r="D84">
         <v>0</v>
       </c>
-      <c r="F84" t="s">
-        <v>223</v>
-      </c>
+      <c r="E84" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="F84" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="G84" s="7">
+        <f>E84*Qct</f>
+        <v>5.8359296844737143</v>
+      </c>
+      <c r="H84" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="I84" s="6"/>
+      <c r="J84" s="6"/>
+      <c r="K84" s="6"/>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
@@ -3086,15 +3102,15 @@
       <c r="D85">
         <v>0</v>
       </c>
-      <c r="E85" s="6">
-        <v>0.05</v>
+      <c r="E85" s="4">
+        <v>0.18</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>260</v>
+        <v>288</v>
       </c>
       <c r="G85" s="7">
         <f>E85*Qct</f>
-        <v>5.8359296844737143</v>
+        <v>21.009346864105368</v>
       </c>
       <c r="H85" s="6" t="s">
         <v>261</v>
@@ -3121,7 +3137,7 @@
         <v>4.5550049155351395E-3</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G86" s="7">
         <f>L81</f>
@@ -3156,7 +3172,7 @@
         <v>216</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H88" s="4"/>
     </row>
@@ -3191,15 +3207,9 @@
       <c r="D90">
         <v>1</v>
       </c>
-      <c r="E90" s="7">
-        <f t="shared" ref="E90:E91" si="0">G90*1.333</f>
-        <v>5.54528</v>
-      </c>
+      <c r="E90" s="19"/>
       <c r="F90" t="s">
         <v>218</v>
-      </c>
-      <c r="G90">
-        <v>4.16</v>
       </c>
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.25">
@@ -3213,7 +3223,7 @@
         <v>1</v>
       </c>
       <c r="E91" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="E90:E91" si="0">G91*1.333</f>
         <v>1.10639</v>
       </c>
       <c r="F91" t="s">
@@ -3278,9 +3288,15 @@
       <c r="D95">
         <v>1</v>
       </c>
-      <c r="E95" s="18"/>
-      <c r="F95" t="s">
-        <v>223</v>
+      <c r="E95" s="7">
+        <f t="shared" ref="E95:E96" si="1">G95*1.333</f>
+        <v>1333</v>
+      </c>
+      <c r="F95" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="G95">
+        <v>1000</v>
       </c>
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.25">
@@ -3294,14 +3310,14 @@
         <v>1</v>
       </c>
       <c r="E96" s="7">
-        <f t="shared" ref="E96:E97" si="1">G96*1.333</f>
-        <v>1333</v>
+        <f t="shared" si="1"/>
+        <v>5.54528</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>260</v>
+        <v>288</v>
       </c>
       <c r="G96">
-        <v>1000</v>
+        <v>4.16</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
@@ -3315,11 +3331,11 @@
         <v>1</v>
       </c>
       <c r="E97" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="E96:E97" si="2">G97*1.333</f>
         <v>0.83979000000000004</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G97">
         <v>0.63</v>
@@ -5083,20 +5099,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="29f62856-1543-49d4-a736-4569d363f533" ContentTypeId="0x0101" PreviousValue="false"/>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C107526348C97345843FB1F7E3F5FF14" ma:contentTypeVersion="20" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1f5efa0b4590ceb4068c523eef838cbf">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xmlns:ns3="http://schemas.microsoft.com/sharepoint.v3" xmlns:ns4="http://schemas.microsoft.com/sharepoint/v3/fields" xmlns:ns5="2ba80736-48fa-4d73-aaff-bacaeeed013a" xmlns:ns6="41d9f072-86bf-4c63-b117-debf50ff4701" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9d32b47d5805bf9e4ccfb00021215c68" ns1:_="" ns2:_="" ns3:_="" ns4:_="" ns5:_="" ns6:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -5569,6 +5571,20 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="29f62856-1543-49d4-a736-4569d363f533" ContentTypeId="0x0101" PreviousValue="false"/>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -5615,22 +5631,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4DC26B68-A11F-428F-9051-23DC6334A810}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C4A2D8C-C5B5-46A0-8FC1-3730CC1A83D7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{90A172F1-773B-43BF-8B86-8CD1537A96AE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5653,6 +5653,22 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C4A2D8C-C5B5-46A0-8FC1-3730CC1A83D7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4DC26B68-A11F-428F-9051-23DC6334A810}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA939294-F21F-45CD-81A6-3A616888DAC5}">
   <ds:schemaRefs>

--- a/Inputs/F_template_parameters_Model.xlsx
+++ b/Inputs/F_template_parameters_Model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usepa-my.sharepoint.com/personal/schlosser_paul_epa_gov/Documents/mcsim-5.6.5/PBPK_Model_Template_Mod/Inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="295" documentId="8_{7F8D94C6-EC2B-4A79-A22A-AD1B7807B962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0CD96151-D1AD-4DB3-9455-7E599C57FEA7}"/>
+  <xr:revisionPtr revIDLastSave="311" documentId="8_{7F8D94C6-EC2B-4A79-A22A-AD1B7807B962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF2E9500-7459-405E-94AF-6D9AA4ACA781}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="24600" windowHeight="13290" xr2:uid="{089E7848-11EB-427A-89EA-83825F220BA0}"/>
+    <workbookView xWindow="3420" yWindow="1830" windowWidth="24600" windowHeight="13290" xr2:uid="{089E7848-11EB-427A-89EA-83825F220BA0}"/>
   </bookViews>
   <sheets>
     <sheet name="Human4yo" sheetId="9" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="291">
   <si>
     <t>Code</t>
   </si>
@@ -922,15 +922,9 @@
     <t>volume above</t>
   </si>
   <si>
-    <t>x Vtf/"Total" volume</t>
-  </si>
-  <si>
     <t>^ "Total" blood flow above</t>
   </si>
   <si>
-    <t>Tissue:plasma coeffs</t>
-  </si>
-  <si>
     <t>Below was copied, with limited translation, from the Jean et al. spreadsheet</t>
   </si>
   <si>
@@ -938,6 +932,15 @@
   </si>
   <si>
     <t>Tota urinary [kidney] CL (L/h) from plasma; multiply by 1.333 to get CL from blood</t>
+  </si>
+  <si>
+    <t>k_met_omc (E46) is also divided by V_omc (E75) and by BW^0.75 to convert CL to a rate 1st order scaled rate constant; it is multiplied by V_omc x BW / BW^0.25 in the code.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      x Vtf/"Total" volume</t>
+  </si>
+  <si>
+    <t>Tissue:plasma coeffs; multiplied by 1.3333 to get tissue:blood PCs</t>
   </si>
 </sst>
 </file>
@@ -947,7 +950,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -955,8 +958,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -984,6 +995,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1094,7 +1111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1130,7 +1147,16 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1267,6 +1293,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1566,7 +1596,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ADCAA70-43B6-4F02-AE2A-67A6EACE5958}">
-  <dimension ref="A1:N105"/>
+  <dimension ref="A1:O105"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -2120,7 +2150,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>52</v>
       </c>
@@ -2134,7 +2164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>53</v>
       </c>
@@ -2148,7 +2178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>54</v>
       </c>
@@ -2166,7 +2196,7 @@
       <c r="I35" s="4"/>
       <c r="J35" s="4"/>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>165</v>
       </c>
@@ -2183,7 +2213,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>56</v>
       </c>
@@ -2197,7 +2227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>237</v>
       </c>
@@ -2211,7 +2241,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>236</v>
       </c>
@@ -2225,7 +2255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>238</v>
       </c>
@@ -2239,7 +2269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>143</v>
       </c>
@@ -2256,7 +2286,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>144</v>
       </c>
@@ -2270,7 +2300,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>145</v>
       </c>
@@ -2284,7 +2314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>146</v>
       </c>
@@ -2301,7 +2331,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>147</v>
       </c>
@@ -2314,8 +2344,18 @@
       <c r="D45">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="F45" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="K45" s="4"/>
+      <c r="L45" s="4"/>
+      <c r="M45" s="4"/>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>203</v>
       </c>
@@ -2337,14 +2377,15 @@
         <v>1.4275558820935248</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H46" s="4"/>
       <c r="I46" s="4"/>
       <c r="J46" s="4"/>
       <c r="K46" s="4"/>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L46" s="4"/>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>148</v>
       </c>
@@ -2361,7 +2402,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>149</v>
       </c>
@@ -2585,7 +2626,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>82</v>
       </c>
@@ -2602,7 +2643,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>89</v>
       </c>
@@ -2622,7 +2663,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>90</v>
       </c>
@@ -2646,7 +2687,7 @@
         <v>0.41599999999999998</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>91</v>
       </c>
@@ -2663,7 +2704,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>92</v>
       </c>
@@ -2680,7 +2721,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>93</v>
       </c>
@@ -2705,7 +2746,7 @@
         <v>1.5933062972602703</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>94</v>
       </c>
@@ -2722,7 +2763,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>95</v>
       </c>
@@ -2739,7 +2780,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>96</v>
       </c>
@@ -2756,7 +2797,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="74" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>97</v>
       </c>
@@ -2779,11 +2820,16 @@
         <f>E74*BW</f>
         <v>1.1200000000000001</v>
       </c>
-      <c r="J74" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="75" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J74" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="K74" s="4"/>
+      <c r="L74" s="4"/>
+      <c r="M74" s="4"/>
+      <c r="N74" s="4"/>
+      <c r="O74" s="4"/>
+    </row>
+    <row r="75" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
         <v>98</v>
       </c>
@@ -2801,7 +2847,7 @@
         <v>5.1037420752262702E-3</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="G75" s="4">
         <f>E75*BW</f>
@@ -2813,7 +2859,7 @@
       </c>
       <c r="L75" s="11"/>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>151</v>
       </c>
@@ -2845,7 +2891,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>104</v>
       </c>
@@ -2880,7 +2926,7 @@
         <v>5.5829400000000009E-4</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>105</v>
       </c>
@@ -2916,7 +2962,7 @@
         <v>7.6608431731805898E-2</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>106</v>
       </c>
@@ -2944,7 +2990,7 @@
         <v>0.18829093630147836</v>
       </c>
     </row>
-    <row r="80" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>107</v>
       </c>
@@ -2971,14 +3017,14 @@
       <c r="H80" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="J80" s="15" t="s">
+      <c r="J80" s="19" t="s">
         <v>279</v>
       </c>
-      <c r="K80" s="13">
+      <c r="K80" s="20">
         <f>SUM(K77:K79)</f>
         <v>6.3856352093374129</v>
       </c>
-      <c r="L80" s="14">
+      <c r="L80" s="21">
         <f>SUM(L77:L79)</f>
         <v>0.26545766203328425</v>
       </c>
@@ -3029,7 +3075,7 @@
         <v>282</v>
       </c>
       <c r="L82" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="M82" s="4"/>
       <c r="N82" s="4"/>
@@ -3054,7 +3100,7 @@
         <v>283</v>
       </c>
       <c r="L83" s="4" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="M83" s="4"/>
       <c r="N83" s="4"/>
@@ -3106,18 +3152,12 @@
         <v>0.18</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="G85" s="7">
         <f>E85*Qct</f>
         <v>21.009346864105368</v>
       </c>
-      <c r="H85" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="I85" s="6"/>
-      <c r="J85" s="6"/>
-      <c r="K85" s="6"/>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
@@ -3171,10 +3211,13 @@
       <c r="F88" t="s">
         <v>216</v>
       </c>
-      <c r="G88" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="H88" s="4"/>
+      <c r="G88" s="22" t="s">
+        <v>290</v>
+      </c>
+      <c r="H88" s="22"/>
+      <c r="I88" s="22"/>
+      <c r="J88" s="22"/>
+      <c r="K88" s="22"/>
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
@@ -3193,7 +3236,7 @@
       <c r="F89" t="s">
         <v>217</v>
       </c>
-      <c r="G89">
+      <c r="G89" s="22">
         <v>0.98</v>
       </c>
     </row>
@@ -3207,10 +3250,11 @@
       <c r="D90">
         <v>1</v>
       </c>
-      <c r="E90" s="19"/>
+      <c r="E90" s="18"/>
       <c r="F90" t="s">
         <v>218</v>
       </c>
+      <c r="G90" s="22"/>
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
@@ -3223,13 +3267,13 @@
         <v>1</v>
       </c>
       <c r="E91" s="7">
-        <f t="shared" ref="E90:E91" si="0">G91*1.333</f>
+        <f t="shared" ref="E91" si="0">G91*1.333</f>
         <v>1.10639</v>
       </c>
       <c r="F91" t="s">
         <v>259</v>
       </c>
-      <c r="G91">
+      <c r="G91" s="22">
         <v>0.83</v>
       </c>
     </row>
@@ -3247,6 +3291,7 @@
       <c r="F92" t="s">
         <v>220</v>
       </c>
+      <c r="G92" s="22"/>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
@@ -3262,6 +3307,7 @@
       <c r="F93" t="s">
         <v>221</v>
       </c>
+      <c r="G93" s="22"/>
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
@@ -3277,6 +3323,7 @@
       <c r="F94" t="s">
         <v>222</v>
       </c>
+      <c r="G94" s="22"/>
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
@@ -3295,7 +3342,7 @@
       <c r="F95" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="G95">
+      <c r="G95" s="22">
         <v>1000</v>
       </c>
     </row>
@@ -3314,9 +3361,9 @@
         <v>5.54528</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>288</v>
-      </c>
-      <c r="G96">
+        <v>286</v>
+      </c>
+      <c r="G96" s="22">
         <v>4.16</v>
       </c>
     </row>
@@ -3331,13 +3378,13 @@
         <v>1</v>
       </c>
       <c r="E97" s="7">
-        <f t="shared" ref="E96:E97" si="2">G97*1.333</f>
+        <f t="shared" ref="E97" si="2">G97*1.333</f>
         <v>0.83979000000000004</v>
       </c>
       <c r="F97" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="G97">
+      <c r="G97" s="22">
         <v>0.63</v>
       </c>
     </row>
@@ -5099,6 +5146,65 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_Source xmlns="http://schemas.microsoft.com/sharepoint/v3/fields" xsi:nil="true"/>
+    <Language xmlns="http://schemas.microsoft.com/sharepoint/v3">English</Language>
+    <j747ac98061d40f0aa7bd47e1db5675d xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </j747ac98061d40f0aa7bd47e1db5675d>
+    <External_x0020_Contributor xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
+    <TaxKeywordTaxHTField xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </TaxKeywordTaxHTField>
+    <Record xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">Shared</Record>
+    <Rights xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
+    <Document_x0020_Creation_x0020_Date xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">2020-10-14T20:30:29+00:00</Document_x0020_Creation_x0020_Date>
+    <EPA_x0020_Office xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
+    <CategoryDescription xmlns="http://schemas.microsoft.com/sharepoint.v3" xsi:nil="true"/>
+    <Identifier xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
+    <_Coverage xmlns="http://schemas.microsoft.com/sharepoint/v3/fields" xsi:nil="true"/>
+    <Creator xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Creator>
+    <EPA_x0020_Related_x0020_Documents xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
+    <EPA_x0020_Contributor xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </EPA_x0020_Contributor>
+    <TaxCatchAll xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
+    <e3f09c3df709400db2417a7161762d62 xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </e3f09c3df709400db2417a7161762d62>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2ba80736-48fa-4d73-aaff-bacaeeed013a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="29f62856-1543-49d4-a736-4569d363f533" ContentTypeId="0x0101" PreviousValue="false"/>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C107526348C97345843FB1F7E3F5FF14" ma:contentTypeVersion="20" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1f5efa0b4590ceb4068c523eef838cbf">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xmlns:ns3="http://schemas.microsoft.com/sharepoint.v3" xmlns:ns4="http://schemas.microsoft.com/sharepoint/v3/fields" xmlns:ns5="2ba80736-48fa-4d73-aaff-bacaeeed013a" xmlns:ns6="41d9f072-86bf-4c63-b117-debf50ff4701" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9d32b47d5805bf9e4ccfb00021215c68" ns1:_="" ns2:_="" ns3:_="" ns4:_="" ns5:_="" ns6:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -5571,66 +5677,38 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="29f62856-1543-49d4-a736-4569d363f533" ContentTypeId="0x0101" PreviousValue="false"/>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA939294-F21F-45CD-81A6-3A616888DAC5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/fields"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4"/>
+    <ds:schemaRef ds:uri="93237db7-bebb-43bb-9414-bc3313990c09"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint.v3"/>
+    <ds:schemaRef ds:uri="2ba80736-48fa-4d73-aaff-bacaeeed013a"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4DC26B68-A11F-428F-9051-23DC6334A810}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Source xmlns="http://schemas.microsoft.com/sharepoint/v3/fields" xsi:nil="true"/>
-    <Language xmlns="http://schemas.microsoft.com/sharepoint/v3">English</Language>
-    <j747ac98061d40f0aa7bd47e1db5675d xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </j747ac98061d40f0aa7bd47e1db5675d>
-    <External_x0020_Contributor xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
-    <TaxKeywordTaxHTField xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </TaxKeywordTaxHTField>
-    <Record xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">Shared</Record>
-    <Rights xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
-    <Document_x0020_Creation_x0020_Date xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">2020-10-14T20:30:29+00:00</Document_x0020_Creation_x0020_Date>
-    <EPA_x0020_Office xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
-    <CategoryDescription xmlns="http://schemas.microsoft.com/sharepoint.v3" xsi:nil="true"/>
-    <Identifier xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
-    <_Coverage xmlns="http://schemas.microsoft.com/sharepoint/v3/fields" xsi:nil="true"/>
-    <Creator xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Creator>
-    <EPA_x0020_Related_x0020_Documents xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
-    <EPA_x0020_Contributor xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </EPA_x0020_Contributor>
-    <TaxCatchAll xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
-    <e3f09c3df709400db2417a7161762d62 xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </e3f09c3df709400db2417a7161762d62>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2ba80736-48fa-4d73-aaff-bacaeeed013a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C4A2D8C-C5B5-46A0-8FC1-3730CC1A83D7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{90A172F1-773B-43BF-8B86-8CD1537A96AE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5651,35 +5729,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C4A2D8C-C5B5-46A0-8FC1-3730CC1A83D7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4DC26B68-A11F-428F-9051-23DC6334A810}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA939294-F21F-45CD-81A6-3A616888DAC5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/fields"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4"/>
-    <ds:schemaRef ds:uri="93237db7-bebb-43bb-9414-bc3313990c09"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint.v3"/>
-    <ds:schemaRef ds:uri="2ba80736-48fa-4d73-aaff-bacaeeed013a"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Inputs/F_template_parameters_Model.xlsx
+++ b/Inputs/F_template_parameters_Model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usepa-my.sharepoint.com/personal/schlosser_paul_epa_gov/Documents/mcsim-5.6.5/PBPK_Model_Template_Mod/Inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="311" documentId="8_{7F8D94C6-EC2B-4A79-A22A-AD1B7807B962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF2E9500-7459-405E-94AF-6D9AA4ACA781}"/>
+  <xr:revisionPtr revIDLastSave="313" documentId="8_{7F8D94C6-EC2B-4A79-A22A-AD1B7807B962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF183F8B-7B2C-4498-A91A-80194D400391}"/>
   <bookViews>
-    <workbookView xWindow="3420" yWindow="1830" windowWidth="24600" windowHeight="13290" xr2:uid="{089E7848-11EB-427A-89EA-83825F220BA0}"/>
+    <workbookView xWindow="1725" yWindow="225" windowWidth="24600" windowHeight="13290" xr2:uid="{089E7848-11EB-427A-89EA-83825F220BA0}"/>
   </bookViews>
   <sheets>
     <sheet name="Human4yo" sheetId="9" r:id="rId1"/>
@@ -5146,65 +5146,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Source xmlns="http://schemas.microsoft.com/sharepoint/v3/fields" xsi:nil="true"/>
-    <Language xmlns="http://schemas.microsoft.com/sharepoint/v3">English</Language>
-    <j747ac98061d40f0aa7bd47e1db5675d xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </j747ac98061d40f0aa7bd47e1db5675d>
-    <External_x0020_Contributor xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
-    <TaxKeywordTaxHTField xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </TaxKeywordTaxHTField>
-    <Record xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">Shared</Record>
-    <Rights xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
-    <Document_x0020_Creation_x0020_Date xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">2020-10-14T20:30:29+00:00</Document_x0020_Creation_x0020_Date>
-    <EPA_x0020_Office xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
-    <CategoryDescription xmlns="http://schemas.microsoft.com/sharepoint.v3" xsi:nil="true"/>
-    <Identifier xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
-    <_Coverage xmlns="http://schemas.microsoft.com/sharepoint/v3/fields" xsi:nil="true"/>
-    <Creator xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Creator>
-    <EPA_x0020_Related_x0020_Documents xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
-    <EPA_x0020_Contributor xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </EPA_x0020_Contributor>
-    <TaxCatchAll xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
-    <e3f09c3df709400db2417a7161762d62 xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </e3f09c3df709400db2417a7161762d62>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2ba80736-48fa-4d73-aaff-bacaeeed013a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="29f62856-1543-49d4-a736-4569d363f533" ContentTypeId="0x0101" PreviousValue="false"/>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C107526348C97345843FB1F7E3F5FF14" ma:contentTypeVersion="20" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1f5efa0b4590ceb4068c523eef838cbf">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xmlns:ns3="http://schemas.microsoft.com/sharepoint.v3" xmlns:ns4="http://schemas.microsoft.com/sharepoint/v3/fields" xmlns:ns5="2ba80736-48fa-4d73-aaff-bacaeeed013a" xmlns:ns6="41d9f072-86bf-4c63-b117-debf50ff4701" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9d32b47d5805bf9e4ccfb00021215c68" ns1:_="" ns2:_="" ns3:_="" ns4:_="" ns5:_="" ns6:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -5677,38 +5618,66 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA939294-F21F-45CD-81A6-3A616888DAC5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/fields"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4"/>
-    <ds:schemaRef ds:uri="93237db7-bebb-43bb-9414-bc3313990c09"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint.v3"/>
-    <ds:schemaRef ds:uri="2ba80736-48fa-4d73-aaff-bacaeeed013a"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="29f62856-1543-49d4-a736-4569d363f533" ContentTypeId="0x0101" PreviousValue="false"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4DC26B68-A11F-428F-9051-23DC6334A810}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C4A2D8C-C5B5-46A0-8FC1-3730CC1A83D7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_Source xmlns="http://schemas.microsoft.com/sharepoint/v3/fields" xsi:nil="true"/>
+    <Language xmlns="http://schemas.microsoft.com/sharepoint/v3">English</Language>
+    <j747ac98061d40f0aa7bd47e1db5675d xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </j747ac98061d40f0aa7bd47e1db5675d>
+    <External_x0020_Contributor xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
+    <TaxKeywordTaxHTField xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </TaxKeywordTaxHTField>
+    <Record xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">Shared</Record>
+    <Rights xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
+    <Document_x0020_Creation_x0020_Date xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">2020-10-14T20:30:29+00:00</Document_x0020_Creation_x0020_Date>
+    <EPA_x0020_Office xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
+    <CategoryDescription xmlns="http://schemas.microsoft.com/sharepoint.v3" xsi:nil="true"/>
+    <Identifier xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
+    <_Coverage xmlns="http://schemas.microsoft.com/sharepoint/v3/fields" xsi:nil="true"/>
+    <Creator xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Creator>
+    <EPA_x0020_Related_x0020_Documents xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
+    <EPA_x0020_Contributor xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </EPA_x0020_Contributor>
+    <TaxCatchAll xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
+    <e3f09c3df709400db2417a7161762d62 xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </e3f09c3df709400db2417a7161762d62>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2ba80736-48fa-4d73-aaff-bacaeeed013a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{90A172F1-773B-43BF-8B86-8CD1537A96AE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5729,4 +5698,35 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C4A2D8C-C5B5-46A0-8FC1-3730CC1A83D7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4DC26B68-A11F-428F-9051-23DC6334A810}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA939294-F21F-45CD-81A6-3A616888DAC5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/fields"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4"/>
+    <ds:schemaRef ds:uri="93237db7-bebb-43bb-9414-bc3313990c09"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint.v3"/>
+    <ds:schemaRef ds:uri="2ba80736-48fa-4d73-aaff-bacaeeed013a"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Inputs/F_template_parameters_Model.xlsx
+++ b/Inputs/F_template_parameters_Model.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="313" documentId="8_{7F8D94C6-EC2B-4A79-A22A-AD1B7807B962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF183F8B-7B2C-4498-A91A-80194D400391}"/>
   <bookViews>
-    <workbookView xWindow="1725" yWindow="225" windowWidth="24600" windowHeight="13290" xr2:uid="{089E7848-11EB-427A-89EA-83825F220BA0}"/>
+    <workbookView xWindow="1080" yWindow="293" windowWidth="24600" windowHeight="13294" xr2:uid="{089E7848-11EB-427A-89EA-83825F220BA0}"/>
   </bookViews>
   <sheets>
     <sheet name="Human4yo" sheetId="9" r:id="rId1"/>
@@ -5146,6 +5146,11 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="29f62856-1543-49d4-a736-4569d363f533" ContentTypeId="0x0101" PreviousValue="false"/>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C107526348C97345843FB1F7E3F5FF14" ma:contentTypeVersion="20" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1f5efa0b4590ceb4068c523eef838cbf">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xmlns:ns3="http://schemas.microsoft.com/sharepoint.v3" xmlns:ns4="http://schemas.microsoft.com/sharepoint/v3/fields" xmlns:ns5="2ba80736-48fa-4d73-aaff-bacaeeed013a" xmlns:ns6="41d9f072-86bf-4c63-b117-debf50ff4701" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9d32b47d5805bf9e4ccfb00021215c68" ns1:_="" ns2:_="" ns3:_="" ns4:_="" ns5:_="" ns6:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -5618,21 +5623,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="29f62856-1543-49d4-a736-4569d363f533" ContentTypeId="0x0101" PreviousValue="false"/>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_Source xmlns="http://schemas.microsoft.com/sharepoint/v3/fields" xsi:nil="true"/>
@@ -5677,7 +5668,24 @@
 </p:properties>
 </file>
 
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C4A2D8C-C5B5-46A0-8FC1-3730CC1A83D7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{90A172F1-773B-43BF-8B86-8CD1537A96AE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5700,23 +5708,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C4A2D8C-C5B5-46A0-8FC1-3730CC1A83D7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4DC26B68-A11F-428F-9051-23DC6334A810}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA939294-F21F-45CD-81A6-3A616888DAC5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -5729,4 +5721,12 @@
     <ds:schemaRef ds:uri="2ba80736-48fa-4d73-aaff-bacaeeed013a"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4DC26B68-A11F-428F-9051-23DC6334A810}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Inputs/F_template_parameters_Model.xlsx
+++ b/Inputs/F_template_parameters_Model.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usepa-my.sharepoint.com/personal/schlosser_paul_epa_gov/Documents/mcsim-5.6.5/PBPK_Model_Template_Mod/Inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="313" documentId="8_{7F8D94C6-EC2B-4A79-A22A-AD1B7807B962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF183F8B-7B2C-4498-A91A-80194D400391}"/>
+  <xr:revisionPtr revIDLastSave="315" documentId="8_{7F8D94C6-EC2B-4A79-A22A-AD1B7807B962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C54FC96-257C-4A8F-903C-D6027B813C66}"/>
   <bookViews>
-    <workbookView xWindow="1080" yWindow="293" windowWidth="24600" windowHeight="13294" xr2:uid="{089E7848-11EB-427A-89EA-83825F220BA0}"/>
+    <workbookView xWindow="5895" yWindow="2640" windowWidth="21600" windowHeight="12585" xr2:uid="{089E7848-11EB-427A-89EA-83825F220BA0}"/>
   </bookViews>
   <sheets>
     <sheet name="Human4yo" sheetId="9" r:id="rId1"/>
@@ -1597,23 +1597,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ADCAA70-43B6-4F02-AE2A-67A6EACE5958}">
   <dimension ref="A1:O105"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="15.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.265625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="51" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" customWidth="1"/>
-    <col min="5" max="5" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.1328125" customWidth="1"/>
+    <col min="5" max="5" width="22.265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.59765625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.5703125" customWidth="1"/>
-    <col min="11" max="11" width="13.140625" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="10" max="10" width="13.59765625" customWidth="1"/>
+    <col min="11" max="11" width="13.1328125" customWidth="1"/>
+    <col min="12" max="12" width="11.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1633,7 +1633,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1644,7 +1644,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -1652,7 +1652,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -1660,7 +1660,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
@@ -1677,7 +1677,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -1694,7 +1694,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
@@ -1708,7 +1708,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
         <v>20</v>
       </c>
@@ -1725,7 +1725,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
         <v>245</v>
       </c>
@@ -1742,7 +1742,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
         <v>132</v>
       </c>
@@ -1759,7 +1759,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
         <v>133</v>
       </c>
@@ -1776,7 +1776,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
         <v>174</v>
       </c>
@@ -1793,7 +1793,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
         <v>178</v>
       </c>
@@ -1810,7 +1810,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
         <v>164</v>
       </c>
@@ -1824,7 +1824,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
         <v>192</v>
       </c>
@@ -1839,7 +1839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
         <v>195</v>
       </c>
@@ -1854,7 +1854,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
         <v>0</v>
       </c>
@@ -1871,7 +1871,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
         <v>69</v>
       </c>
@@ -1891,7 +1891,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
         <v>27</v>
       </c>
@@ -1905,7 +1905,7 @@
         <v>0.74</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
         <v>29</v>
       </c>
@@ -1916,7 +1916,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
         <v>226</v>
       </c>
@@ -1930,7 +1930,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A23" s="1" t="s">
         <v>31</v>
       </c>
@@ -1941,7 +1941,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A24" s="1" t="s">
         <v>32</v>
       </c>
@@ -1962,7 +1962,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A25" s="1" t="s">
         <v>42</v>
       </c>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="J25" s="4"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A26" s="1" t="s">
         <v>138</v>
       </c>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="J26" s="4"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A27" s="1" t="s">
         <v>139</v>
       </c>
@@ -2039,7 +2039,7 @@
       <c r="H27" s="4"/>
       <c r="I27" s="4"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A28" s="1" t="s">
         <v>47</v>
       </c>
@@ -2062,7 +2062,7 @@
       <c r="H28" s="4"/>
       <c r="I28" s="4"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A29" s="1" t="s">
         <v>140</v>
       </c>
@@ -2088,7 +2088,7 @@
       <c r="H29" s="4"/>
       <c r="I29" s="4"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A30" s="1" t="s">
         <v>141</v>
       </c>
@@ -2111,7 +2111,7 @@
       <c r="H30" s="4"/>
       <c r="I30" s="4"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A31" s="1" t="s">
         <v>142</v>
       </c>
@@ -2133,7 +2133,7 @@
       </c>
       <c r="H31" s="4"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A32" s="1" t="s">
         <v>51</v>
       </c>
@@ -2150,7 +2150,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A33" s="1" t="s">
         <v>52</v>
       </c>
@@ -2164,7 +2164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A34" s="1" t="s">
         <v>53</v>
       </c>
@@ -2178,7 +2178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A35" s="1" t="s">
         <v>54</v>
       </c>
@@ -2196,7 +2196,7 @@
       <c r="I35" s="4"/>
       <c r="J35" s="4"/>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A36" s="1" t="s">
         <v>165</v>
       </c>
@@ -2213,7 +2213,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A37" s="1" t="s">
         <v>56</v>
       </c>
@@ -2227,7 +2227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A38" s="1" t="s">
         <v>237</v>
       </c>
@@ -2241,7 +2241,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A39" s="1" t="s">
         <v>236</v>
       </c>
@@ -2255,7 +2255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A40" s="1" t="s">
         <v>238</v>
       </c>
@@ -2269,7 +2269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A41" s="1" t="s">
         <v>143</v>
       </c>
@@ -2286,7 +2286,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A42" s="1" t="s">
         <v>144</v>
       </c>
@@ -2300,7 +2300,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A43" s="1" t="s">
         <v>145</v>
       </c>
@@ -2314,7 +2314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A44" s="1" t="s">
         <v>146</v>
       </c>
@@ -2331,7 +2331,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A45" s="1" t="s">
         <v>147</v>
       </c>
@@ -2355,7 +2355,7 @@
       <c r="L45" s="4"/>
       <c r="M45" s="4"/>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A46" s="1" t="s">
         <v>203</v>
       </c>
@@ -2385,7 +2385,7 @@
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A47" s="1" t="s">
         <v>148</v>
       </c>
@@ -2402,7 +2402,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A48" s="1" t="s">
         <v>149</v>
       </c>
@@ -2416,7 +2416,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A49" s="1" t="s">
         <v>150</v>
       </c>
@@ -2430,7 +2430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A50" s="1" t="s">
         <v>37</v>
       </c>
@@ -2441,7 +2441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A51" s="1" t="s">
         <v>168</v>
       </c>
@@ -2452,7 +2452,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A52" s="1" t="s">
         <v>39</v>
       </c>
@@ -2463,7 +2463,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A53" s="1" t="s">
         <v>184</v>
       </c>
@@ -2477,7 +2477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A54" s="1" t="s">
         <v>160</v>
       </c>
@@ -2491,7 +2491,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A55" s="1" t="s">
         <v>161</v>
       </c>
@@ -2502,7 +2502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A56" s="1" t="s">
         <v>198</v>
       </c>
@@ -2516,7 +2516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A57" s="1" t="s">
         <v>200</v>
       </c>
@@ -2530,7 +2530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A58" s="1" t="s">
         <v>231</v>
       </c>
@@ -2547,7 +2547,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A59" s="1" t="s">
         <v>41</v>
       </c>
@@ -2558,7 +2558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A61" s="1" t="s">
         <v>0</v>
       </c>
@@ -2575,7 +2575,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A62" s="1" t="s">
         <v>79</v>
       </c>
@@ -2592,7 +2592,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A63" s="1" t="s">
         <v>134</v>
       </c>
@@ -2609,7 +2609,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A64" s="1" t="s">
         <v>136</v>
       </c>
@@ -2626,7 +2626,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A65" s="1" t="s">
         <v>82</v>
       </c>
@@ -2643,7 +2643,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A66" s="1" t="s">
         <v>89</v>
       </c>
@@ -2663,7 +2663,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A67" s="1" t="s">
         <v>90</v>
       </c>
@@ -2687,7 +2687,7 @@
         <v>0.41599999999999998</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A68" s="1" t="s">
         <v>91</v>
       </c>
@@ -2704,7 +2704,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A69" s="1" t="s">
         <v>92</v>
       </c>
@@ -2721,7 +2721,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A70" s="1" t="s">
         <v>93</v>
       </c>
@@ -2746,7 +2746,7 @@
         <v>1.5933062972602703</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A71" s="1" t="s">
         <v>94</v>
       </c>
@@ -2763,7 +2763,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A72" s="1" t="s">
         <v>95</v>
       </c>
@@ -2780,7 +2780,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A73" s="1" t="s">
         <v>96</v>
       </c>
@@ -2797,7 +2797,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="74" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:15" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A74" s="1" t="s">
         <v>97</v>
       </c>
@@ -2829,7 +2829,7 @@
       <c r="N74" s="4"/>
       <c r="O74" s="4"/>
     </row>
-    <row r="75" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:15" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A75" s="1" t="s">
         <v>98</v>
       </c>
@@ -2859,7 +2859,7 @@
       </c>
       <c r="L75" s="11"/>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A76" s="1" t="s">
         <v>151</v>
       </c>
@@ -2891,7 +2891,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A77" s="1" t="s">
         <v>104</v>
       </c>
@@ -2926,7 +2926,7 @@
         <v>5.5829400000000009E-4</v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A78" s="1" t="s">
         <v>105</v>
       </c>
@@ -2962,7 +2962,7 @@
         <v>7.6608431731805898E-2</v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A79" s="1" t="s">
         <v>106</v>
       </c>
@@ -2990,7 +2990,7 @@
         <v>0.18829093630147836</v>
       </c>
     </row>
-    <row r="80" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:15" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A80" s="1" t="s">
         <v>107</v>
       </c>
@@ -3029,7 +3029,7 @@
         <v>0.26545766203328425</v>
       </c>
     </row>
-    <row r="81" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:14" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A81" s="1" t="s">
         <v>108</v>
       </c>
@@ -3055,7 +3055,7 @@
         <v>0.53165376798990405</v>
       </c>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A82" s="1" t="s">
         <v>109</v>
       </c>
@@ -3080,7 +3080,7 @@
       <c r="M82" s="4"/>
       <c r="N82" s="4"/>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A83" s="1" t="s">
         <v>110</v>
       </c>
@@ -3105,7 +3105,7 @@
       <c r="M83" s="4"/>
       <c r="N83" s="4"/>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A84" s="1" t="s">
         <v>111</v>
       </c>
@@ -3135,7 +3135,7 @@
       <c r="J84" s="6"/>
       <c r="K84" s="6"/>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A85" s="1" t="s">
         <v>112</v>
       </c>
@@ -3159,7 +3159,7 @@
         <v>21.009346864105368</v>
       </c>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A86" s="1" t="s">
         <v>153</v>
       </c>
@@ -3184,7 +3184,7 @@
         <v>0.53165376798990405</v>
       </c>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A87" s="1" t="s">
         <v>121</v>
       </c>
@@ -3198,7 +3198,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A88" s="1" t="s">
         <v>122</v>
       </c>
@@ -3219,7 +3219,7 @@
       <c r="J88" s="22"/>
       <c r="K88" s="22"/>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A89" s="1" t="s">
         <v>123</v>
       </c>
@@ -3240,7 +3240,7 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A90" s="1" t="s">
         <v>124</v>
       </c>
@@ -3256,7 +3256,7 @@
       </c>
       <c r="G90" s="22"/>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A91" s="1" t="s">
         <v>125</v>
       </c>
@@ -3277,7 +3277,7 @@
         <v>0.83</v>
       </c>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A92" s="1" t="s">
         <v>126</v>
       </c>
@@ -3293,7 +3293,7 @@
       </c>
       <c r="G92" s="22"/>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A93" s="1" t="s">
         <v>127</v>
       </c>
@@ -3309,7 +3309,7 @@
       </c>
       <c r="G93" s="22"/>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A94" s="1" t="s">
         <v>128</v>
       </c>
@@ -3325,7 +3325,7 @@
       </c>
       <c r="G94" s="22"/>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A95" s="1" t="s">
         <v>129</v>
       </c>
@@ -3346,7 +3346,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A96" s="1" t="s">
         <v>130</v>
       </c>
@@ -3367,7 +3367,7 @@
         <v>4.16</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A97" s="1" t="s">
         <v>156</v>
       </c>
@@ -3388,7 +3388,7 @@
         <v>0.63</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A99" s="1" t="s">
         <v>0</v>
       </c>
@@ -3405,7 +3405,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A100" s="1" t="s">
         <v>34</v>
       </c>
@@ -3413,7 +3413,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A102" s="1" t="s">
         <v>0</v>
       </c>
@@ -3428,7 +3428,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A103" s="1" t="s">
         <v>73</v>
       </c>
@@ -3436,7 +3436,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A104" s="1" t="s">
         <v>75</v>
       </c>
@@ -3444,7 +3444,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A105" s="1" t="s">
         <v>77</v>
       </c>
@@ -3484,21 +3484,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2530FCFD-82CD-436F-B981-3C7AACA19280}">
   <dimension ref="A1:J105"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="15.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.265625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="51" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" customWidth="1"/>
-    <col min="5" max="5" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.1328125" customWidth="1"/>
+    <col min="5" max="5" width="22.265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.59765625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.5703125" customWidth="1"/>
+    <col min="10" max="10" width="13.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3518,7 +3518,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -3529,7 +3529,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -3537,7 +3537,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -3545,7 +3545,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
@@ -3562,7 +3562,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -3579,7 +3579,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
@@ -3593,7 +3593,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
         <v>20</v>
       </c>
@@ -3610,7 +3610,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
         <v>245</v>
       </c>
@@ -3625,7 +3625,7 @@
       </c>
       <c r="E9" s="2"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
         <v>132</v>
       </c>
@@ -3639,7 +3639,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
         <v>133</v>
       </c>
@@ -3653,7 +3653,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
         <v>174</v>
       </c>
@@ -3670,7 +3670,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
         <v>178</v>
       </c>
@@ -3687,7 +3687,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
         <v>164</v>
       </c>
@@ -3701,7 +3701,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
         <v>192</v>
       </c>
@@ -3716,7 +3716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
         <v>195</v>
       </c>
@@ -3731,7 +3731,7 @@
         <v>0.95599999999999996</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
         <v>0</v>
       </c>
@@ -3748,7 +3748,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
         <v>69</v>
       </c>
@@ -3768,7 +3768,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
         <v>27</v>
       </c>
@@ -3782,7 +3782,7 @@
         <v>0.74</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
         <v>29</v>
       </c>
@@ -3793,7 +3793,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
         <v>226</v>
       </c>
@@ -3807,7 +3807,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A23" s="1" t="s">
         <v>31</v>
       </c>
@@ -3818,7 +3818,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A24" s="1" t="s">
         <v>32</v>
       </c>
@@ -3839,7 +3839,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A25" s="1" t="s">
         <v>42</v>
       </c>
@@ -3856,7 +3856,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A26" s="1" t="s">
         <v>138</v>
       </c>
@@ -3879,7 +3879,7 @@
       <c r="H26" s="4"/>
       <c r="I26" s="4"/>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A27" s="1" t="s">
         <v>139</v>
       </c>
@@ -3903,7 +3903,7 @@
       <c r="H27" s="4"/>
       <c r="I27" s="4"/>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A28" s="1" t="s">
         <v>47</v>
       </c>
@@ -3926,7 +3926,7 @@
       <c r="H28" s="4"/>
       <c r="I28" s="4"/>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A29" s="1" t="s">
         <v>140</v>
       </c>
@@ -3949,7 +3949,7 @@
       <c r="H29" s="4"/>
       <c r="I29" s="4"/>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A30" s="1" t="s">
         <v>141</v>
       </c>
@@ -3972,7 +3972,7 @@
       <c r="H30" s="4"/>
       <c r="I30" s="4"/>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A31" s="1" t="s">
         <v>142</v>
       </c>
@@ -3986,7 +3986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A32" s="1" t="s">
         <v>51</v>
       </c>
@@ -4003,7 +4003,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A33" s="1" t="s">
         <v>52</v>
       </c>
@@ -4017,7 +4017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A34" s="1" t="s">
         <v>53</v>
       </c>
@@ -4031,7 +4031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A35" s="1" t="s">
         <v>54</v>
       </c>
@@ -4045,7 +4045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A36" s="1" t="s">
         <v>165</v>
       </c>
@@ -4066,7 +4066,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A37" s="1" t="s">
         <v>56</v>
       </c>
@@ -4087,7 +4087,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A38" s="1" t="s">
         <v>237</v>
       </c>
@@ -4101,7 +4101,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A39" s="1" t="s">
         <v>236</v>
       </c>
@@ -4115,7 +4115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A40" s="1" t="s">
         <v>238</v>
       </c>
@@ -4129,7 +4129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A41" s="1" t="s">
         <v>143</v>
       </c>
@@ -4146,7 +4146,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A42" s="1" t="s">
         <v>144</v>
       </c>
@@ -4160,7 +4160,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A43" s="1" t="s">
         <v>145</v>
       </c>
@@ -4174,7 +4174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A44" s="1" t="s">
         <v>146</v>
       </c>
@@ -4191,7 +4191,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A45" s="1" t="s">
         <v>147</v>
       </c>
@@ -4205,7 +4205,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A46" s="1" t="s">
         <v>203</v>
       </c>
@@ -4227,7 +4227,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A47" s="1" t="s">
         <v>148</v>
       </c>
@@ -4244,7 +4244,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A48" s="1" t="s">
         <v>149</v>
       </c>
@@ -4258,7 +4258,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A49" s="1" t="s">
         <v>150</v>
       </c>
@@ -4272,7 +4272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A50" s="1" t="s">
         <v>37</v>
       </c>
@@ -4283,7 +4283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A51" s="1" t="s">
         <v>168</v>
       </c>
@@ -4294,7 +4294,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A52" s="1" t="s">
         <v>39</v>
       </c>
@@ -4305,7 +4305,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A53" s="1" t="s">
         <v>184</v>
       </c>
@@ -4319,7 +4319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A54" s="1" t="s">
         <v>160</v>
       </c>
@@ -4333,7 +4333,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A55" s="1" t="s">
         <v>161</v>
       </c>
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A56" s="1" t="s">
         <v>198</v>
       </c>
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A57" s="1" t="s">
         <v>200</v>
       </c>
@@ -4372,7 +4372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A58" s="1" t="s">
         <v>231</v>
       </c>
@@ -4389,7 +4389,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A59" s="1" t="s">
         <v>41</v>
       </c>
@@ -4400,7 +4400,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A61" s="1" t="s">
         <v>0</v>
       </c>
@@ -4417,7 +4417,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A62" s="1" t="s">
         <v>79</v>
       </c>
@@ -4434,7 +4434,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A63" s="1" t="s">
         <v>134</v>
       </c>
@@ -4451,7 +4451,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A64" s="1" t="s">
         <v>136</v>
       </c>
@@ -4468,7 +4468,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A65" s="1" t="s">
         <v>82</v>
       </c>
@@ -4485,7 +4485,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A66" s="1" t="s">
         <v>89</v>
       </c>
@@ -4502,7 +4502,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A67" s="1" t="s">
         <v>90</v>
       </c>
@@ -4522,7 +4522,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A68" s="1" t="s">
         <v>91</v>
       </c>
@@ -4542,7 +4542,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A69" s="1" t="s">
         <v>92</v>
       </c>
@@ -4559,7 +4559,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A70" s="1" t="s">
         <v>93</v>
       </c>
@@ -4579,7 +4579,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A71" s="1" t="s">
         <v>94</v>
       </c>
@@ -4596,7 +4596,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A72" s="1" t="s">
         <v>95</v>
       </c>
@@ -4613,7 +4613,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A73" s="1" t="s">
         <v>96</v>
       </c>
@@ -4630,7 +4630,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A74" s="1" t="s">
         <v>97</v>
       </c>
@@ -4647,7 +4647,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A75" s="1" t="s">
         <v>98</v>
       </c>
@@ -4667,7 +4667,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A76" s="1" t="s">
         <v>151</v>
       </c>
@@ -4687,7 +4687,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A77" s="1" t="s">
         <v>104</v>
       </c>
@@ -4704,7 +4704,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A78" s="1" t="s">
         <v>105</v>
       </c>
@@ -4724,7 +4724,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A79" s="1" t="s">
         <v>106</v>
       </c>
@@ -4744,7 +4744,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A80" s="1" t="s">
         <v>107</v>
       </c>
@@ -4764,7 +4764,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A81" s="1" t="s">
         <v>108</v>
       </c>
@@ -4781,7 +4781,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A82" s="1" t="s">
         <v>109</v>
       </c>
@@ -4798,7 +4798,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A83" s="1" t="s">
         <v>110</v>
       </c>
@@ -4815,7 +4815,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A84" s="1" t="s">
         <v>111</v>
       </c>
@@ -4832,7 +4832,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A85" s="1" t="s">
         <v>112</v>
       </c>
@@ -4858,7 +4858,7 @@
       <c r="I85" s="6"/>
       <c r="J85" s="6"/>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A86" s="1" t="s">
         <v>153</v>
       </c>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="H86" s="5"/>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A87" s="1" t="s">
         <v>121</v>
       </c>
@@ -4897,7 +4897,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A88" s="1" t="s">
         <v>122</v>
       </c>
@@ -4911,7 +4911,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A89" s="1" t="s">
         <v>123</v>
       </c>
@@ -4928,7 +4928,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A90" s="1" t="s">
         <v>124</v>
       </c>
@@ -4945,7 +4945,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A91" s="1" t="s">
         <v>125</v>
       </c>
@@ -4962,7 +4962,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A92" s="1" t="s">
         <v>126</v>
       </c>
@@ -4976,7 +4976,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A93" s="1" t="s">
         <v>127</v>
       </c>
@@ -4990,7 +4990,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A94" s="1" t="s">
         <v>128</v>
       </c>
@@ -5004,7 +5004,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A95" s="1" t="s">
         <v>129</v>
       </c>
@@ -5018,7 +5018,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A96" s="1" t="s">
         <v>130</v>
       </c>
@@ -5035,7 +5035,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A97" s="1" t="s">
         <v>156</v>
       </c>
@@ -5052,7 +5052,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A99" s="1" t="s">
         <v>0</v>
       </c>
@@ -5069,7 +5069,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A100" s="1" t="s">
         <v>34</v>
       </c>
@@ -5077,7 +5077,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A102" s="1" t="s">
         <v>0</v>
       </c>
@@ -5092,7 +5092,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A103" s="1" t="s">
         <v>73</v>
       </c>
@@ -5100,7 +5100,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A104" s="1" t="s">
         <v>75</v>
       </c>
@@ -5108,7 +5108,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A105" s="1" t="s">
         <v>77</v>
       </c>
@@ -5151,6 +5151,60 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_Source xmlns="http://schemas.microsoft.com/sharepoint/v3/fields" xsi:nil="true"/>
+    <Language xmlns="http://schemas.microsoft.com/sharepoint/v3">English</Language>
+    <j747ac98061d40f0aa7bd47e1db5675d xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </j747ac98061d40f0aa7bd47e1db5675d>
+    <External_x0020_Contributor xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
+    <TaxKeywordTaxHTField xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </TaxKeywordTaxHTField>
+    <Record xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">Shared</Record>
+    <Rights xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
+    <Document_x0020_Creation_x0020_Date xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">2020-10-14T20:30:29+00:00</Document_x0020_Creation_x0020_Date>
+    <EPA_x0020_Office xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
+    <CategoryDescription xmlns="http://schemas.microsoft.com/sharepoint.v3" xsi:nil="true"/>
+    <Identifier xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
+    <_Coverage xmlns="http://schemas.microsoft.com/sharepoint/v3/fields" xsi:nil="true"/>
+    <Creator xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Creator>
+    <EPA_x0020_Related_x0020_Documents xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
+    <EPA_x0020_Contributor xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </EPA_x0020_Contributor>
+    <TaxCatchAll xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
+    <e3f09c3df709400db2417a7161762d62 xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </e3f09c3df709400db2417a7161762d62>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2ba80736-48fa-4d73-aaff-bacaeeed013a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C107526348C97345843FB1F7E3F5FF14" ma:contentTypeVersion="20" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1f5efa0b4590ceb4068c523eef838cbf">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xmlns:ns3="http://schemas.microsoft.com/sharepoint.v3" xmlns:ns4="http://schemas.microsoft.com/sharepoint/v3/fields" xmlns:ns5="2ba80736-48fa-4d73-aaff-bacaeeed013a" xmlns:ns6="41d9f072-86bf-4c63-b117-debf50ff4701" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9d32b47d5805bf9e4ccfb00021215c68" ns1:_="" ns2:_="" ns3:_="" ns4:_="" ns5:_="" ns6:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -5623,60 +5677,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Source xmlns="http://schemas.microsoft.com/sharepoint/v3/fields" xsi:nil="true"/>
-    <Language xmlns="http://schemas.microsoft.com/sharepoint/v3">English</Language>
-    <j747ac98061d40f0aa7bd47e1db5675d xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </j747ac98061d40f0aa7bd47e1db5675d>
-    <External_x0020_Contributor xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
-    <TaxKeywordTaxHTField xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </TaxKeywordTaxHTField>
-    <Record xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">Shared</Record>
-    <Rights xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
-    <Document_x0020_Creation_x0020_Date xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">2020-10-14T20:30:29+00:00</Document_x0020_Creation_x0020_Date>
-    <EPA_x0020_Office xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
-    <CategoryDescription xmlns="http://schemas.microsoft.com/sharepoint.v3" xsi:nil="true"/>
-    <Identifier xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
-    <_Coverage xmlns="http://schemas.microsoft.com/sharepoint/v3/fields" xsi:nil="true"/>
-    <Creator xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Creator>
-    <EPA_x0020_Related_x0020_Documents xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
-    <EPA_x0020_Contributor xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </EPA_x0020_Contributor>
-    <TaxCatchAll xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xsi:nil="true"/>
-    <e3f09c3df709400db2417a7161762d62 xmlns="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </e3f09c3df709400db2417a7161762d62>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2ba80736-48fa-4d73-aaff-bacaeeed013a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C4A2D8C-C5B5-46A0-8FC1-3730CC1A83D7}">
   <ds:schemaRefs>
@@ -5686,6 +5686,29 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4DC26B68-A11F-428F-9051-23DC6334A810}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA939294-F21F-45CD-81A6-3A616888DAC5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/fields"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4"/>
+    <ds:schemaRef ds:uri="93237db7-bebb-43bb-9414-bc3313990c09"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint.v3"/>
+    <ds:schemaRef ds:uri="2ba80736-48fa-4d73-aaff-bacaeeed013a"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{90A172F1-773B-43BF-8B86-8CD1537A96AE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5706,27 +5729,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA939294-F21F-45CD-81A6-3A616888DAC5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/fields"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4"/>
-    <ds:schemaRef ds:uri="93237db7-bebb-43bb-9414-bc3313990c09"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint.v3"/>
-    <ds:schemaRef ds:uri="2ba80736-48fa-4d73-aaff-bacaeeed013a"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4DC26B68-A11F-428F-9051-23DC6334A810}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>